--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -8,6 +8,8 @@
     <sheet name="4 ตั้งค่าเริ่มต้นเชิงพาณิชย์" sheetId="4" r:id="rId4"/>
     <sheet name="5 ตรวจรับก่อนใช้จริง" sheetId="5" r:id="rId5"/>
     <sheet name="6 แก้ปัญหา" sheetId="6" r:id="rId6"/>
+    <sheet name="7 คำสั่งที่ต้องใช้" sheetId="7" r:id="rId7"/>
+    <sheet name="8 ความปลอดภัย" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -135,103 +137,115 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 วิธีใช้ · 2 เช็คลิสต์ติดตั้ง · 3 ค่าที่ต้องตั้ง · 4 ตั้งค่าเริ่มต้นเชิงพาณิชย์ · 5 ตรวจรับก่อนใช้จริง · 6 แก้ปัญหา</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ค่าที่จำเป็นจริง ๆ มีแค่</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">NEXT_PUBLIC_SUPABASE_URL และ NEXT_PUBLIC_SUPABASE_ANON_KEY — ที่เหลือเป็นของเสริมทั้งหมด</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">1 วิธีใช้ · 2 เช็คลิสต์ติดตั้ง · 3 ค่าที่ต้องตั้ง · 4 ตั้งค่าเริ่มต้นเชิงพาณิชย์ · 5 ตรวจรับก่อนใช้จริง · 6 แก้ปัญหา · 7 คำสั่งที่ต้องใช้ · 8 ความปลอดภัย</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ชีตที่ต้องทำให้ครบก่อนเปิดใช้จริง</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ชีต 2 (ติดตั้ง) · ชีต 4 (ตั้งค่าเชิงพาณิชย์) · ชีต 5 (ตรวจรับ) · ชีต 8 (ความปลอดภัย เฉพาะข้อที่เป็นบังคับ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">ค่าที่จำเป็นจริง ๆ มีแค่</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEXT_PUBLIC_SUPABASE_URL และ NEXT_PUBLIC_SUPABASE_ANON_KEY — ที่เหลือเป็นของเสริมทั้งหมด</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สามข้อที่พลาดบ่อยที่สุด</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="2">
+      <c r="B11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 ลืมติ๊ก Auto Confirm User · 2 ใส่ตัวแปรแล้วไม่ได้ Redeploy · 3 รัน schema.sql ไม่จบแล้วไม่ได้ดูตารางสรุป</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">จำนวนตารางฐานข้อมูล</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">44 ตาราง — สร้างครบจากไฟล์ supabase/schema.sql ไฟล์เดียว</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">จำนวนหน้าจอ</t>
+          <t xml:space="preserve">จำนวนตารางฐานข้อมูล</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">56 หน้า</t>
+          <t xml:space="preserve">44 ตาราง — สร้างครบจากไฟล์ supabase/schema.sql ไฟล์เดียว</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รุ่นของโปรแกรมตอนสร้างไฟล์นี้</t>
+          <t xml:space="preserve">จำนวนหน้าจอ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFAU 3.3 · รอบ 92 (2026-09-12)</t>
+          <t xml:space="preserve">56 หน้า</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างไฟล์นี้เมื่อ</t>
+          <t xml:space="preserve">รุ่นของโปรแกรมตอนสร้างไฟล์นี้</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">OFAU 3.3 · รอบ 93 (2026-09-12)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือฉบับเต็ม</t>
+          <t xml:space="preserve">สร้างไฟล์นี้เมื่อ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Docs/คู่มือการติดตั้ง.md (อธิบายเหตุผลและวิธีแก้ปัญหาแบบละเอียด)</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">คู่มือฉบับเต็ม</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Docs/คู่มือการติดตั้ง.md (อธิบายเหตุผลและวิธีแก้ปัญหาแบบละเอียด)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สร้างไฟล์นี้ใหม่</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr" s="2">
+      <c r="B18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">node tools/make-setup-xlsx.mjs</t>
         </is>
@@ -1476,7 +1490,7 @@
       </c>
       <c r="G27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 92 (2026-09-12))</t>
+          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 93 (2026-09-12))</t>
         </is>
       </c>
       <c r="H27" t="inlineStr" s="2">
@@ -3075,4 +3089,1361 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="64" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="4" max="4" width="72" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>คำสั่ง</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t>ทำอะไร</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t>ใช้ตอนไหน</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>ข้อควรรู้</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ติดตั้งและรันในเครื่อง</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">npm install</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลงไลบรารีที่โปรเจกต์ต้องใช้ (next, react, react-dom)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ครั้งแรกที่ clone โค้ดมา และเมื่อ package.json เปลี่ยน</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างโฟลเดอร์ node_modules ซึ่งไม่ขึ้น git · ต้องมี Node.js 18.18 ขึ้นไป</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">npm run dev</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รันเว็บในเครื่องตัวเองที่ http://localhost:3000  (สั่งจริงคือ next dev)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตอนแก้โค้ดแล้วอยากเห็นผลทันทีโดยไม่ต้อง deploy</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ต้องสั่ง npm install ก่อนหนึ่งครั้ง และต้องมีไฟล์ .env.local · แก้ไฟล์แล้วหน้าเว็บรีเฟรชให้เอง</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">npm run build</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างไฟล์สำหรับใช้งานจริง และจับ error ที่ตอนเขียนโค้ดไม่ฟ้อง  (สั่งจริงคือ next build)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ก่อน push ขึ้น main ถ้าอยากมั่นใจว่า Vercel จะ build ผ่าน</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Vercel สั่งคำสั่งนี้ให้เองทุกครั้งที่ push · build ไม่ผ่านแปลว่าเว็บจะไม่อัปเดต</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">npm run start</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รันไฟล์ที่ build แล้วแบบเดียวกับบนเซิร์ฟเวอร์จริง  (สั่งจริงคือ next start)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อยากทดสอบความเร็วจริงในเครื่อง ไม่ใช่โหมดแก้โค้ด</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ต้องสั่ง npm run build ก่อนเสมอ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">npm run check</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตรวจความเรียบร้อยทั้งโปรเจกต์ 26 หมวด  (สั่งจริงคือ node tools/check.mjs)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทุกครั้งก่อน commit — เป็นคำสั่งที่ใช้บ่อยที่สุด</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทำงานโดยอ่านไฟล์ตรง ๆ ไม่ต้องมี node_modules · จับบั๊กที่ไม่มีใครฟ้องตอนแก้โค้ดแต่จอขาวตอนใช้จริง</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">งานกับ Git และการ deploy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">git status</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ดูว่าแก้ไฟล์อะไรไปบ้างและยังไม่ได้ commit</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ก่อน commit ทุกครั้ง</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใช้ตรวจด้วยว่าไฟล์ .env.local ไม่ได้หลุดเข้ามาในรายการ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">git add -A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เอาไฟล์ที่แก้ทั้งหมดเข้าคิว commit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หลังตรวจ git status แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">git commit -m "ข้อความ"</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บันทึกการแก้ไขหนึ่งชุดพร้อมคำอธิบาย</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เมื่อแก้เรื่องหนึ่งจบ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เขียนข้อความเป็นภาษาคน บอกว่าแก้อะไรและทำไม</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">git push</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ส่งขึ้น GitHub — Vercel จะ deploy ให้เองทันที</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เมื่อพร้อมให้ของขึ้นใช้งานจริง</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">push ขึ้น main คือการ deploy ขึ้นเว็บจริง ตรวจให้ดีก่อน</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">git pull</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ดึงโค้ดรุ่นใหม่จาก GitHub ลงเครื่อง</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ก่อนเริ่มแก้โค้ดทุกครั้ง</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ถ้ารุ่นใหม่มีตารางเพิ่ม ต้องรัน supabase/schema.sql ซ้ำด้วย</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">git log --oneline -10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ดูประวัติสิบรายการล่าสุด</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อยากรู้ว่ารุ่นล่าสุดแก้อะไรไป</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">git checkout &lt;ชื่อไฟล์&gt;</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยกเลิกการแก้ไฟล์นั้น กลับไปเป็นรุ่นที่ commit ไว้ล่าสุด</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แก้พังแล้วอยากถอย</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ระวัง — สิ่งที่แก้ไปหายทันทีและกู้ไม่ได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สคริปต์ของโครงงาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">node tools/check.mjs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตัวตรวจความเรียบร้อยทั้งโปรเจกต์ (เรียกผ่าน npm run check ก็ได้)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทุกครั้งก่อน commit</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์ tools/check.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">node tools/make-process-xlsx.mjs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้าง Docs/ProjectProcess.xlsx (กระบวนการสร้างโครงงาน)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทุกครั้งที่ส่งงานรอบใหม่</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์ tools/make-process-xlsx.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">node tools/make-setup-xlsx.mjs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างไฟล์เช็คลิสต์การติดตั้งนี้ใหม่</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เมื่อเพิ่มหน้าจอ เพิ่มตัวแปร หรือเปลี่ยนขั้นตอนติดตั้ง</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์ tools/make-setup-xlsx.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">node tools/make-thai-address.mjs</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างตารางเขตปกครองไทย (จังหวัด อำเภอ ตำบล รหัสไปรษณีย์)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เมื่อมีการเปลี่ยนแปลงเขตปกครอง — นาน ๆ ครั้ง</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์ tools/make-thai-address.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">node tools/make-voc-manual.mjs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างคู่มือหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เมื่อแก้เนื้อหาคู่มือในหมวดนั้น</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์ tools/make-voc-manual.mjs</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">powershell -File tools/trim-logo.ps1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างไฟล์โลโก้และไอคอนทุกขนาดจากภาพต้นฉบับไฟล์เดียว</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เมื่อเปลี่ยนโลโก้</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์ tools/trim-logo.ps1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">งานกับฐานข้อมูล</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รัน supabase/schema.sql</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างหรืออัปเดตฐานข้อมูลทั้งหมด</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ครั้งแรกที่ติดตั้ง และทุกครั้งที่อัปเดตเป็นรุ่นที่มีตารางเพิ่ม</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทำที่ Supabase &gt; SQL Editor · คัดลอกทั้งไฟล์ · รันซ้ำได้ ไม่ลบข้อมูลเดิม · ต้องดูตารางสรุปท้ายผล</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">select * from ชื่อตาราง limit 20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ดูข้อมูลในตารางตรง ๆ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตอนไล่หาสาเหตุว่าข้อมูลเข้าไปจริงหรือไม่</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทำที่ Supabase &gt; SQL Editor · อ่านอย่างเดียว ปลอดภัย</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">notify pgrst, 'reload schema'</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สั่งให้ API รู้จักตารางที่เพิ่งสร้าง</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เมื่อขึ้น error PGRST205 ว่าหาตารางไม่เจอ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อยู่ท้าย schema.sql อยู่แล้ว สั่งแยกเมื่อจำเป็นเท่านั้น</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="66" customWidth="1"/>
+    <col min="4" max="4" width="80" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>หมวด</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t>เรื่องที่ต้องทำ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t>ทำอย่างไร</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>ถ้าไม่ทำจะเกิดอะไร</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>ตรวจอย่างไรว่าทำแล้ว</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>ระดับ</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>สถานะ</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t>ผู้ตรวจ</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t>วันที่ตรวจ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กุญแจและความลับ</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แยกกุญแจสองชนิดให้ออก</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">anon public key เปิดเผยได้ ใส่ในหน้าเว็บได้ · service_role key ข้ามทุกสิทธิ์ ห้ามออกจากฝั่งเซิร์ฟเวอร์</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใส่ service_role ในหน้าเว็บเมื่อไร ใครเปิดเว็บก็อ่าน แก้ และลบข้อมูลทั้งระบบได้ทันที</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปิด Vercel &gt; Environment Variables ดูว่าไม่มีตัวไหนขึ้นต้นด้วย NEXT_PUBLIC_ แล้วเก็บค่าลับไว้</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กุญแจและความลับ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ชื่อตัวแปรลับห้ามขึ้นต้นด้วย NEXT_PUBLIC_</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Next.js ฝังเฉพาะตัวแปรที่ขึ้นต้นด้วย NEXT_PUBLIC_ ลงในไฟล์ที่เบราว์เซอร์โหลด</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เผลอตั้งชื่อผิดครั้งเดียว กุญแจหลุดทันทีและไม่มีอะไรเตือน</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตัวตรวจของระบบ (npm run check) เฝ้าข้อนี้ให้อยู่แล้ว</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กุญแจและความลับ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์ .env.local ต้องไม่ขึ้น git</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตรวจว่า .gitignore มีบรรทัด .env*.local</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หลุดขึ้น git แล้วลบ commit ทีหลังก็ยังอยู่ในประวัติ ใครก็ย้อนดูได้</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สั่ง git status แล้วต้องไม่เห็นไฟล์ .env.local ในรายการ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กุญแจและความลับ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยนกุญแจทันทีเมื่อสงสัยว่าหลุด</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Supabase &gt; Project Settings &gt; API &gt; Reset ของกุญแจนั้น แล้วใส่ค่าใหม่ที่ Vercel และ Redeploy</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กุญแจที่หลุดแล้วใช้ได้ตลอดไปจนกว่าจะเปลี่ยน การลบไฟล์หรือลบ commit ไม่ได้ทำให้กุญแจใช้ไม่ได้</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลองใช้กุญแจเก่าแล้วต้องถูกปฏิเสธ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับเมื่อเกิดเหตุ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บัญชีผู้ใช้</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หนึ่งคนหนึ่งบัญชี ห้ามใช้ร่วมกัน</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทุกเอกสารบันทึกว่าใครเป็นคนทำ ใช้บัญชีร่วมกันแล้วตรวจสอบย้อนหลังไม่ได้เลยว่าใครทำอะไร</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปิดรายงานแล้วเห็นชื่อผู้ทำเป็นคนละคนตามความจริง</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บัญชีผู้ใช้</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปิดการสมัครสมาชิกเองเมื่อไม่ใช้แล้ว</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Supabase &gt; Authentication &gt; Sign In / Providers &gt; Email &gt; ปิด Allow new users to sign up</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปิดค้างไว้ ใครก็สมัครเข้ามาเองได้ แล้วเห็นข้อมูลทั้งระบบ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลองสมัครจากหน้าเพิ่มผู้ใช้งานแล้วต้องถูกปฏิเสธ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับหลังสร้างผู้ใช้ครบ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บัญชีผู้ใช้</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปิดใช้งานบัญชีคนที่ลาออกทันที</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตั้งสถานะเป็นปิดใช้งานในหน้าทะเบียนผู้ใช้ และลบผู้ใช้ที่ Supabase &gt; Authentication &gt; Users</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บัญชีที่ค้างไว้ยังล็อกอินได้และยังเห็นข้อมูลทั้งหมด</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลองล็อกอินด้วยบัญชีนั้นแล้วต้องเข้าไม่ได้</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับเมื่อมีคนออก</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บัญชีผู้ใช้</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แอดมินต้องมีมากกว่าหนึ่งคน</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตั้งบทบาทแอดมินให้อย่างน้อยสองคนที่หน้ากำหนดสิทธิการใช้งาน</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แอดมินคนเดียวลาออกหรือลืมรหัสผ่าน จะไม่มีใครตั้งสิทธิให้ใครได้อีกเลย</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หน้ากำหนดสิทธิแสดงแอดมินอย่างน้อยสองคน</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แนะนำ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สิทธิการใช้งาน</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เข้าใจว่าสิทธิหน้าจอคุมอะไรได้จริง</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สิทธิรายหน้าจอคุมว่าใครเห็นเมนูไหนและกดแก้ไขได้ไหม</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เป็นการคุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล — คนที่ล็อกอินแล้วยังอ่านและเขียนตารางข้อมูลผ่าน API ได้ทุกตาราง เพราะ policy ของตารางข้อมูลตั้งไว้ว่าผู้ที่ล็อกอินแล้วเข้าถึงได้</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ให้บัญชีระบบเฉพาะคนที่ไว้ใจให้เห็นข้อมูลทั้งหมดได้ · ถ้าต้องกั้นถึงระดับข้อมูล ต้องเขียน policy ตามบทบาทเพิ่มทุกตาราง</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับให้รู้ไว้</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สิทธิการใช้งาน</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตั้งสิทธิตามงานที่ทำจริง</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">คลังไม่ควรเห็นหน้าตั้งราคา ฝ่ายขายไม่ควรแก้ผังคลัง</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลดการกดผิดหน้าโดยไม่ตั้งใจ ซึ่งเป็นสาเหตุของข้อมูลเพี้ยนที่พบบ่อยกว่าการจงใจ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ล็อกอินด้วยบัญชีพนักงานแล้วเห็นเฉพาะเมนูที่ควรเห็น</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แนะนำ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ฐานข้อมูล</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สองด่านของ Supabase ต้องผ่านทั้งคู่</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ด่านแรกคือ GRANT ระดับตาราง ด่านสองคือ RLS policy</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไม่ผ่านด่านแรกได้ HTTP 403 · ไม่ผ่านด่านสองอ่านได้ผลว่างหรือเขียนไม่ได้ · อาการต่างกัน แก้คนละที่</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รัน supabase/schema.sql ทั้งไฟล์แล้วตารางสรุปขึ้น ผ่าน ครบทุกแถว</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ฐานข้อมูล</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เก็บรหัสผ่านฐานข้อมูลไว้ให้ปลอดภัย</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รหัสที่ตั้งตอนสร้างโปรเจกต์ Supabase</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใช้ต่อฐานข้อมูลตรง ๆ ได้ ซึ่งข้ามทุกสิทธิ์เหมือน service_role key</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เก็บในที่เก็บรหัสผ่าน ไม่ใช่ในไฟล์โน้ตหรือแชท</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ฐานข้อมูล</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รหัสผ่านการเชื่อมต่อฐานข้อมูลภายนอก ไม่ต้องเก็บขึ้นฐานข้อมูล</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ที่หน้าเชื่อมต่อฐานข้อมูลภายนอก ค่าเริ่มต้นคือเก็บไว้ในเครื่องที่กรอกเท่านั้น</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทุกคนที่ล็อกอินอ่านตารางนั้นได้ และค่าที่เก็บจะติดไปกับไฟล์สำรองข้อมูลด้วย</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไม่ติ๊กช่องให้เก็บขึ้นฐานข้อมูล เว้นแต่จำเป็นจริง ๆ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แนะนำ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์สำรองข้อมูล</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์สำรองคือข้อมูลจริงทั้งก้อน</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">มีทั้งทะเบียนลูกค้า ที่อยู่ เลขผู้เสียภาษี ราคาขาย และเอกสารทุกใบ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หลุดออกไปเท่ากับฐานข้อมูลหลุด ต่างกันแค่ไม่มีกุญแจติดไปด้วย</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เก็บในที่ที่คุมสิทธิ์ได้ ไม่ส่งผ่านแชทหรืออีเมลโดยไม่ใส่รหัส</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์สำรองข้อมูล</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สำรองตามรอบ และทดลองกู้คืนจริง</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สำรองก่อนอัปเดตรุ่นใหญ่ทุกครั้ง และตามรอบที่กำหนด</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง และจะรู้ตอนที่สายเกินไปเสมอ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เคยกู้คืนสำเร็จมาแล้วอย่างน้อยหนึ่งครั้ง</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การเชื่อมต่อภายนอก</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตัวรับข้อความจากไลน์ตรวจลายเซ็นทุกคำขอ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ระบบตรวจ HMAC-SHA256 ด้วย LINE_CHANNEL_SECRET ก่อนรับข้อความทุกครั้ง</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ที่อยู่ webhook เป็น URL สาธารณะ ใครเดาถูกก็ยิงเข้ามาได้ ไม่ตรวจแล้วจะมีคำสั่งซื้อปลอมเต็มระบบ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลองยิงคำขอมั่วไปที่ webhook แล้วต้องได้ 401 กลับมา</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับถ้าเปิดใช้</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การเชื่อมต่อภายนอก</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อความจากไลน์ไม่กลายเป็นเอกสารเอง</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ต้องมีคนกดตรวจและยืนยันที่หน้าคำสั่งซื้อเสมอ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อมูลจากนอกระบบที่กลายเป็นเอกสารเองได้ คือช่องให้คนนอกสั่งงานระบบเรา</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ระบบออกแบบมาแบบนี้อยู่แล้ว และตัวตรวจเฝ้าไว้ไม่ให้มีใครทำทางลัด</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การเชื่อมต่อภายนอก</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">จำกัดคนที่ใช้ผู้ช่วย AI ได้</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตั้ง CHAT_ALLOWED_EMAILS ให้เป็นรายชื่อที่อนุญาต</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผู้ช่วย AI ใช้โควตาที่เสียเงิน และคำถามอาจมีข้อมูลของกิจการปนไป</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ล็อกอินด้วยบัญชีที่ไม่อยู่ในรายการแล้วใช้ไม่ได้</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แนะนำ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การใช้งานประจำวัน</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยนรหัสผ่านของตัวเองเป็นระยะ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทำที่หน้าเปลี่ยนรหัสผ่านในโปรแกรม</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รหัสผ่านที่ใช้มานานและใช้ซ้ำกับเว็บอื่น คือทางเข้าที่ง่ายที่สุด</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทุกคนเคยเปลี่ยนอย่างน้อยหนึ่งครั้ง</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แนะนำ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การใช้งานประจำวัน</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ออกจากระบบเมื่อใช้เครื่องร่วมกัน</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">โดยเฉพาะเครื่องที่หน้าร้านหรือในคลัง</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ระบบจำการล็อกอินไว้ในเครื่อง ใครมานั่งต่อก็ใช้สิทธิของคนก่อนหน้าได้ทันที</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปิดเบราว์เซอร์แล้วเปิดใหม่ ต้องขึ้นหน้าล็อกอิน</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แนะนำ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">การใช้งานประจำวัน</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อย่าใช้เว็บผ่าน Wi-Fi สาธารณะโดยไม่จำเป็น</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เว็บใช้ HTTPS อยู่แล้วจาก Vercel</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อมูลระหว่างทางปลอดภัย แต่เครื่องที่ติดมัลแวร์หรือมีคนดูจอ ยังเป็นความเสี่ยงที่ HTTPS ช่วยไม่ได้</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใช้เครื่องของกิจการเป็นหลัก</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แนะนำ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -157,95 +157,107 @@
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค่าที่จำเป็นจริง ๆ มีแค่</t>
+          <t xml:space="preserve">คำสั่งเดียวที่ควรจำ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEXT_PUBLIC_SUPABASE_URL และ NEXT_PUBLIC_SUPABASE_ANON_KEY — ที่เหลือเป็นของเสริมทั้งหมด</t>
+          <t xml:space="preserve">npm run setup — ตรวจให้ว่าติดตั้งถึงไหนแล้ว และบอกเป็นข้อ ๆ ว่าเหลืออะไรต้องทำ · สั่งได้ตลอดทุกขั้น</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">ค่าที่จำเป็นจริง ๆ มีแค่</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEXT_PUBLIC_SUPABASE_URL และ NEXT_PUBLIC_SUPABASE_ANON_KEY — ที่เหลือเป็นของเสริมทั้งหมด</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สามข้อที่พลาดบ่อยที่สุด</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr" s="2">
+      <c r="B12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 ลืมติ๊ก Auto Confirm User · 2 ใส่ตัวแปรแล้วไม่ได้ Redeploy · 3 รัน schema.sql ไม่จบแล้วไม่ได้ดูตารางสรุป</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">จำนวนตารางฐานข้อมูล</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">44 ตาราง — สร้างครบจากไฟล์ supabase/schema.sql ไฟล์เดียว</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">จำนวนหน้าจอ</t>
+          <t xml:space="preserve">จำนวนตารางฐานข้อมูล</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">56 หน้า</t>
+          <t xml:space="preserve">44 ตาราง — สร้างครบจากไฟล์ supabase/schema.sql ไฟล์เดียว</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รุ่นของโปรแกรมตอนสร้างไฟล์นี้</t>
+          <t xml:space="preserve">จำนวนหน้าจอ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFAU 3.3 · รอบ 93 (2026-09-12)</t>
+          <t xml:space="preserve">56 หน้า</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างไฟล์นี้เมื่อ</t>
+          <t xml:space="preserve">รุ่นของโปรแกรมตอนสร้างไฟล์นี้</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">OFAU 3.3 · รอบ 94 (2026-09-12)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือฉบับเต็ม</t>
+          <t xml:space="preserve">สร้างไฟล์นี้เมื่อ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Docs/คู่มือการติดตั้ง.md (อธิบายเหตุผลและวิธีแก้ปัญหาแบบละเอียด)</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">คู่มือฉบับเต็ม</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Docs/คู่มือการติดตั้ง.md (อธิบายเหตุผลและวิธีแก้ปัญหาแบบละเอียด)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สร้างไฟล์นี้ใหม่</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr" s="2">
+      <c r="B19" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">node tools/make-setup-xlsx.mjs</t>
         </is>
@@ -1105,37 +1117,37 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">D. เอาโค้ดขึ้น GitHub</t>
+          <t xml:space="preserve">C. สร้างฐานข้อมูล Supabase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้าง repository ใหม่</t>
+          <t xml:space="preserve">ตรวจว่าฐานข้อมูลพร้อมแล้วจริง</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">github.com &gt; New repository</t>
+          <t xml:space="preserve">เครื่องตัวเอง</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตั้งเป็น Private ถ้าเป็นงานของกิจการ</t>
+          <t xml:space="preserve">สั่ง npm run setup -- --init แล้วใส่ค่าสองตัวลงไฟล์ .env.local · สั่ง npm run setup อีกรอบ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โค้ดของระบบการค้าไม่ควรเปิดสาธารณะ แม้กุญแจจะไม่ได้อยู่ในโค้ดก็ตาม</t>
+          <t xml:space="preserve">ตรวจของจริงถึง Supabase ว่าตารางครบและกุญแจใช้ได้ · รู้ผลตั้งแต่ตอนนี้ ดีกว่าไปรู้ตอนขึ้น Vercel แล้วล็อกอินไม่ได้</t>
         </is>
       </c>
       <c r="G19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ได้ที่อยู่ repo มาแล้ว</t>
+          <t xml:space="preserve">ผลลัพธ์ขึ้นว่า พร้อมใช้งาน — ติดตั้งครบแล้ว</t>
         </is>
       </c>
       <c r="H19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บังคับ</t>
+          <t xml:space="preserve">แนะนำอย่างยิ่ง</t>
         </is>
       </c>
       <c r="I19" t="inlineStr" s="2">
@@ -1155,27 +1167,27 @@
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">push โค้ดขึ้น repo</t>
+          <t xml:space="preserve">สร้าง repository ใหม่</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เครื่องตัวเอง</t>
+          <t xml:space="preserve">github.com &gt; New repository</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">git init · git add . · git commit · git branch -M main · git remote add origin · git push -u origin main</t>
+          <t xml:space="preserve">ตั้งเป็น Private ถ้าเป็นงานของกิจการ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vercel อ่านโค้ดจาก GitHub ไม่ได้อัปโหลดไฟล์ตรง</t>
+          <t xml:space="preserve">โค้ดของระบบการค้าไม่ควรเปิดสาธารณะ แม้กุญแจจะไม่ได้อยู่ในโค้ดก็ตาม</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปิดหน้า repo บนเว็บแล้วเห็นไฟล์ครบ</t>
+          <t xml:space="preserve">ได้ที่อยู่ repo มาแล้ว</t>
         </is>
       </c>
       <c r="H20" t="inlineStr" s="2">
@@ -1200,27 +1212,27 @@
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจว่าไม่มีไฟล์ .env.local ขึ้นไปด้วย</t>
+          <t xml:space="preserve">push โค้ดขึ้น repo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้า repo บน GitHub</t>
+          <t xml:space="preserve">เครื่องตัวเอง</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดูรายการไฟล์ในหน้าแรกของ repo</t>
+          <t xml:space="preserve">git init · git add . · git commit · git branch -M main · git remote add origin · git push -u origin main</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ถ้าหลุดขึ้นไปแล้ว ต้องไปสร้าง anon key ใหม่ที่ Supabase ทันที ลบไฟล์อย่างเดียวไม่พอ</t>
+          <t xml:space="preserve">Vercel อ่านโค้ดจาก GitHub ไม่ได้อัปโหลดไฟล์ตรง</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ไม่เห็นไฟล์ .env.local ในรายการ</t>
+          <t xml:space="preserve">เปิดหน้า repo บนเว็บแล้วเห็นไฟล์ครบ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr" s="2">
@@ -1240,32 +1252,32 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">E. ตั้งค่าและ deploy บน Vercel</t>
+          <t xml:space="preserve">D. เอาโค้ดขึ้น GitHub</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างโปรเจกต์จาก repo</t>
+          <t xml:space="preserve">ตรวจว่าไม่มีไฟล์ .env.local ขึ้นไปด้วย</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vercel &gt; Add New &gt; Project</t>
+          <t xml:space="preserve">หน้า repo บน GitHub</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลือก repo ที่เพิ่ง push · Framework ขึ้น Next.js เอง ไม่ต้องแก้</t>
+          <t xml:space="preserve">ดูรายการไฟล์ในหน้าแรกของ repo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vercel อ่านค่าจาก package.json ได้เองทั้งหมด</t>
+          <t xml:space="preserve">ถ้าหลุดขึ้นไปแล้ว ต้องไปสร้าง anon key ใหม่ที่ Supabase ทันที ลบไฟล์อย่างเดียวไม่พอ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เห็นหน้าตั้งค่าโปรเจกต์ของ Vercel</t>
+          <t xml:space="preserve">ไม่เห็นไฟล์ .env.local ในรายการ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr" s="2">
@@ -1290,27 +1302,27 @@
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ใส่ NEXT_PUBLIC_SUPABASE_URL</t>
+          <t xml:space="preserve">สร้างโปรเจกต์จาก repo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vercel &gt; Project Settings &gt; Environment Variables</t>
+          <t xml:space="preserve">Vercel &gt; Add New &gt; Project</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">วาง Project URL ที่คัดลอกไว้</t>
+          <t xml:space="preserve">เลือก repo ที่เพิ่ง push · Framework ขึ้น Next.js เอง ไม่ต้องแก้</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ไม่ใส่แล้วหน้าล็อกอินจะขึ้นกล่องเหลืองว่ายังไม่ได้ตั้งค่า Supabase</t>
+          <t xml:space="preserve">Vercel อ่านค่าจาก package.json ได้เองทั้งหมด</t>
         </is>
       </c>
       <c r="G23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ติ๊กครบทั้ง Production, Preview และ Development</t>
+          <t xml:space="preserve">เห็นหน้าตั้งค่าโปรเจกต์ของ Vercel</t>
         </is>
       </c>
       <c r="H23" t="inlineStr" s="2">
@@ -1335,7 +1347,7 @@
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ใส่ NEXT_PUBLIC_SUPABASE_ANON_KEY</t>
+          <t xml:space="preserve">ใส่ NEXT_PUBLIC_SUPABASE_URL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -1345,17 +1357,17 @@
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">วาง anon public key ที่คัดลอกไว้</t>
+          <t xml:space="preserve">วาง Project URL ที่คัดลอกไว้</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เหมือนข้อบน · ชื่อต้องสะกดตรงเป๊ะรวมทั้งคำว่า NEXT_PUBLIC_</t>
+          <t xml:space="preserve">ไม่ใส่แล้วหน้าล็อกอินจะขึ้นกล่องเหลืองว่ายังไม่ได้ตั้งค่า Supabase</t>
         </is>
       </c>
       <c r="G24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ติ๊กครบทั้งสาม environment</t>
+          <t xml:space="preserve">ติ๊กครบทั้ง Production, Preview และ Development</t>
         </is>
       </c>
       <c r="H24" t="inlineStr" s="2">
@@ -1380,27 +1392,27 @@
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สั่ง Deploy</t>
+          <t xml:space="preserve">ใส่ NEXT_PUBLIC_SUPABASE_ANON_KEY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vercel &gt; Deployments</t>
+          <t xml:space="preserve">Vercel &gt; Project Settings &gt; Environment Variables</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">กด Deploy (หรือ Redeploy ถ้าเคย deploy ไปก่อนใส่ตัวแปร)</t>
+          <t xml:space="preserve">วาง anon public key ที่คัดลอกไว้</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวแปรที่ขึ้นต้นด้วย NEXT_PUBLIC_ ถูกฝังลงไฟล์ตอน build ไม่ใช่ตอนรัน ใส่แล้วต้อง deploy ใหม่เสมอ</t>
+          <t xml:space="preserve">เหมือนข้อบน · ชื่อต้องสะกดตรงเป๊ะรวมทั้งคำว่า NEXT_PUBLIC_</t>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สถานะขึ้น Ready</t>
+          <t xml:space="preserve">ติ๊กครบทั้งสาม environment</t>
         </is>
       </c>
       <c r="H25" t="inlineStr" s="2">
@@ -1425,27 +1437,27 @@
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปิดเว็บแล้วล็อกอิน</t>
+          <t xml:space="preserve">สั่ง Deploy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">โดเมนของ Vercel</t>
+          <t xml:space="preserve">Vercel &gt; Deployments</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ใช้อีเมลและรหัสผ่านที่สร้างไว้ในช่วง C</t>
+          <t xml:space="preserve">กด Deploy (หรือ Redeploy ถ้าเคย deploy ไปก่อนใส่ตัวแปร)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เป็นการพิสูจน์ว่าทั้งสามส่วนต่อกันติดแล้ว (เว็บ + ฐานข้อมูล + ระบบล็อกอิน)</t>
+          <t xml:space="preserve">ตัวแปรที่ขึ้นต้นด้วย NEXT_PUBLIC_ ถูกฝังลงไฟล์ตอน build ไม่ใช่ตอนรัน ใส่แล้วต้อง deploy ใหม่เสมอ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เข้าหน้าแดชบอร์ดได้ และเมนูซ้ายขึ้นครบ</t>
+          <t xml:space="preserve">สถานะขึ้น Ready</t>
         </is>
       </c>
       <c r="H26" t="inlineStr" s="2">
@@ -1470,35 +1482,80 @@
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">เปิดเว็บแล้วล็อกอิน</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">โดเมนของ Vercel</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใช้อีเมลและรหัสผ่านที่สร้างไว้ในช่วง C</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เป็นการพิสูจน์ว่าทั้งสามส่วนต่อกันติดแล้ว (เว็บ + ฐานข้อมูล + ระบบล็อกอิน)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เข้าหน้าแดชบอร์ดได้ และเมนูซ้ายขึ้นครบ</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บังคับ</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รอทำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">E. ตั้งค่าและ deploy บน Vercel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">ตรวจเลขรุ่นท้ายเมนูซ้าย</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr" s="2">
+      <c r="D28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ในโปรแกรม</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr" s="2">
+      <c r="E28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ต้องตรงกับ APP_BUILD ในไฟล์ lib/constants.js</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr" s="2">
+      <c r="F28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ถ้าไม่ตรง แปลว่าเบราว์เซอร์ยังถือไฟล์เก่าอยู่ หรือ Vercel ยัง deploy ไม่เสร็จ</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 93 (2026-09-12))</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr" s="2">
+      <c r="G28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 94 (2026-09-12))</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">แนะนำ</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr" s="2">
+      <c r="I28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">รอทำ</t>
         </is>
@@ -3242,361 +3299,405 @@
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานกับ Git และการ deploy</t>
+          <t xml:space="preserve">npm run setup</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตรวจว่าติดตั้งถึงไหนแล้ว และบอกเป็นข้อ ๆ ว่าต้องทำอะไรต่อ  (สั่งจริงคือ node tools/setup.mjs)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตอนติดตั้งครั้งแรก และทุกครั้งที่ระบบมีปัญหาแล้วไม่รู้ว่าพลาดตรงไหน</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตรวจของจริงถึง Supabase เลย ไม่ได้เดาจากไฟล์ · เติม --init ให้สร้างไฟล์ .env.local จากไฟล์ตัวอย่างให้ด้วย</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">git status</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ดูว่าแก้ไฟล์อะไรไปบ้างและยังไม่ได้ commit</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ก่อน commit ทุกครั้ง</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ใช้ตรวจด้วยว่าไฟล์ .env.local ไม่ได้หลุดเข้ามาในรายการ</t>
+          <t xml:space="preserve">งานกับ Git และการ deploy</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">git add -A</t>
+          <t xml:space="preserve">git status</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เอาไฟล์ที่แก้ทั้งหมดเข้าคิว commit</t>
+          <t xml:space="preserve">ดูว่าแก้ไฟล์อะไรไปบ้างและยังไม่ได้ commit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หลังตรวจ git status แล้ว</t>
+          <t xml:space="preserve">ก่อน commit ทุกครั้ง</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใช้ตรวจด้วยว่าไฟล์ .env.local ไม่ได้หลุดเข้ามาในรายการ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">git commit -m "ข้อความ"</t>
+          <t xml:space="preserve">git add -A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกการแก้ไขหนึ่งชุดพร้อมคำอธิบาย</t>
+          <t xml:space="preserve">เอาไฟล์ที่แก้ทั้งหมดเข้าคิว commit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เมื่อแก้เรื่องหนึ่งจบ</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">เขียนข้อความเป็นภาษาคน บอกว่าแก้อะไรและทำไม</t>
+          <t xml:space="preserve">หลังตรวจ git status แล้ว</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">git push</t>
+          <t xml:space="preserve">git commit -m "ข้อความ"</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ส่งขึ้น GitHub — Vercel จะ deploy ให้เองทันที</t>
+          <t xml:space="preserve">บันทึกการแก้ไขหนึ่งชุดพร้อมคำอธิบาย</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เมื่อพร้อมให้ของขึ้นใช้งานจริง</t>
+          <t xml:space="preserve">เมื่อแก้เรื่องหนึ่งจบ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">push ขึ้น main คือการ deploy ขึ้นเว็บจริง ตรวจให้ดีก่อน</t>
+          <t xml:space="preserve">เขียนข้อความเป็นภาษาคน บอกว่าแก้อะไรและทำไม</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">git pull</t>
+          <t xml:space="preserve">git push</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดึงโค้ดรุ่นใหม่จาก GitHub ลงเครื่อง</t>
+          <t xml:space="preserve">ส่งขึ้น GitHub — Vercel จะ deploy ให้เองทันที</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ก่อนเริ่มแก้โค้ดทุกครั้ง</t>
+          <t xml:space="preserve">เมื่อพร้อมให้ของขึ้นใช้งานจริง</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ถ้ารุ่นใหม่มีตารางเพิ่ม ต้องรัน supabase/schema.sql ซ้ำด้วย</t>
+          <t xml:space="preserve">push ขึ้น main คือการ deploy ขึ้นเว็บจริง ตรวจให้ดีก่อน</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">git log --oneline -10</t>
+          <t xml:space="preserve">git pull</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดูประวัติสิบรายการล่าสุด</t>
+          <t xml:space="preserve">ดึงโค้ดรุ่นใหม่จาก GitHub ลงเครื่อง</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อยากรู้ว่ารุ่นล่าสุดแก้อะไรไป</t>
+          <t xml:space="preserve">ก่อนเริ่มแก้โค้ดทุกครั้ง</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ถ้ารุ่นใหม่มีตารางเพิ่ม ต้องรัน supabase/schema.sql ซ้ำด้วย</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">git checkout &lt;ชื่อไฟล์&gt;</t>
+          <t xml:space="preserve">git log --oneline -10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยกเลิกการแก้ไฟล์นั้น กลับไปเป็นรุ่นที่ commit ไว้ล่าสุด</t>
+          <t xml:space="preserve">ดูประวัติสิบรายการล่าสุด</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้พังแล้วอยากถอย</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ระวัง — สิ่งที่แก้ไปหายทันทีและกู้ไม่ได้</t>
+          <t xml:space="preserve">อยากรู้ว่ารุ่นล่าสุดแก้อะไรไป</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สคริปต์ของโครงงาน</t>
+          <t xml:space="preserve">git checkout &lt;ชื่อไฟล์&gt;</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยกเลิกการแก้ไฟล์นั้น กลับไปเป็นรุ่นที่ commit ไว้ล่าสุด</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แก้พังแล้วอยากถอย</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ระวัง — สิ่งที่แก้ไปหายทันทีและกู้ไม่ได้</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">node tools/check.mjs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ตัวตรวจความเรียบร้อยทั้งโปรเจกต์ (เรียกผ่าน npm run check ก็ได้)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ทุกครั้งก่อน commit</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ไฟล์ tools/check.mjs</t>
+          <t xml:space="preserve">สคริปต์ของโครงงาน</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">node tools/make-process-xlsx.mjs</t>
+          <t xml:space="preserve">node tools/check.mjs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้าง Docs/ProjectProcess.xlsx (กระบวนการสร้างโครงงาน)</t>
+          <t xml:space="preserve">ตัวตรวจความเรียบร้อยทั้งโปรเจกต์ (เรียกผ่าน npm run check ก็ได้)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทุกครั้งที่ส่งงานรอบใหม่</t>
+          <t xml:space="preserve">ทุกครั้งก่อน commit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ไฟล์ tools/make-process-xlsx.mjs</t>
+          <t xml:space="preserve">ไฟล์ tools/check.mjs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">node tools/make-setup-xlsx.mjs</t>
+          <t xml:space="preserve">node tools/make-process-xlsx.mjs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างไฟล์เช็คลิสต์การติดตั้งนี้ใหม่</t>
+          <t xml:space="preserve">สร้าง Docs/ProjectProcess.xlsx (กระบวนการสร้างโครงงาน)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เมื่อเพิ่มหน้าจอ เพิ่มตัวแปร หรือเปลี่ยนขั้นตอนติดตั้ง</t>
+          <t xml:space="preserve">ทุกครั้งที่ส่งงานรอบใหม่</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ไฟล์ tools/make-setup-xlsx.mjs</t>
+          <t xml:space="preserve">ไฟล์ tools/make-process-xlsx.mjs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">node tools/make-thai-address.mjs</t>
+          <t xml:space="preserve">node tools/make-setup-xlsx.mjs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างตารางเขตปกครองไทย (จังหวัด อำเภอ ตำบล รหัสไปรษณีย์)</t>
+          <t xml:space="preserve">สร้างไฟล์เช็คลิสต์การติดตั้งนี้ใหม่</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เมื่อมีการเปลี่ยนแปลงเขตปกครอง — นาน ๆ ครั้ง</t>
+          <t xml:space="preserve">เมื่อเพิ่มหน้าจอ เพิ่มตัวแปร หรือเปลี่ยนขั้นตอนติดตั้ง</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ไฟล์ tools/make-thai-address.mjs</t>
+          <t xml:space="preserve">ไฟล์ tools/make-setup-xlsx.mjs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">node tools/make-voc-manual.mjs</t>
+          <t xml:space="preserve">node tools/make-thai-address.mjs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างคู่มือหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
+          <t xml:space="preserve">สร้างตารางเขตปกครองไทย (จังหวัด อำเภอ ตำบล รหัสไปรษณีย์)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เมื่อแก้เนื้อหาคู่มือในหมวดนั้น</t>
+          <t xml:space="preserve">เมื่อมีการเปลี่ยนแปลงเขตปกครอง — นาน ๆ ครั้ง</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ไฟล์ tools/make-voc-manual.mjs</t>
+          <t xml:space="preserve">ไฟล์ tools/make-thai-address.mjs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">powershell -File tools/trim-logo.ps1</t>
+          <t xml:space="preserve">node tools/make-voc-manual.mjs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างไฟล์โลโก้และไอคอนทุกขนาดจากภาพต้นฉบับไฟล์เดียว</t>
+          <t xml:space="preserve">สร้างคู่มือหมวดการรับฟังลูกค้าเป็นไฟล์ Word</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เมื่อเปลี่ยนโลโก้</t>
+          <t xml:space="preserve">เมื่อแก้เนื้อหาคู่มือในหมวดนั้น</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ไฟล์ tools/trim-logo.ps1</t>
+          <t xml:space="preserve">ไฟล์ tools/make-voc-manual.mjs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">งานกับฐานข้อมูล</t>
+          <t xml:space="preserve">node tools/setup.mjs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตัวช่วยติดตั้ง — บอกว่าตอนนี้ถึงขั้นไหนและต้องทำอะไรต่อ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตอนติดตั้งครั้งแรก และตอนที่ระบบมีปัญหาแล้วไม่รู้ว่าพลาดตรงไหน</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์ tools/setup.mjs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รัน supabase/schema.sql</t>
+          <t xml:space="preserve">powershell -File tools/trim-logo.ps1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างหรืออัปเดตฐานข้อมูลทั้งหมด</t>
+          <t xml:space="preserve">สร้างไฟล์โลโก้และไอคอนทุกขนาดจากภาพต้นฉบับไฟล์เดียว</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ครั้งแรกที่ติดตั้ง และทุกครั้งที่อัปเดตเป็นรุ่นที่มีตารางเพิ่ม</t>
+          <t xml:space="preserve">เมื่อเปลี่ยนโลโก้</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ทำที่ Supabase &gt; SQL Editor · คัดลอกทั้งไฟล์ · รันซ้ำได้ ไม่ลบข้อมูลเดิม · ต้องดูตารางสรุปท้ายผล</t>
+          <t xml:space="preserve">ไฟล์ tools/trim-logo.ps1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">select * from ชื่อตาราง limit 20</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ดูข้อมูลในตารางตรง ๆ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ตอนไล่หาสาเหตุว่าข้อมูลเข้าไปจริงหรือไม่</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">ทำที่ Supabase &gt; SQL Editor · อ่านอย่างเดียว ปลอดภัย</t>
+          <t xml:space="preserve">งานกับฐานข้อมูล</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">รัน supabase/schema.sql</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างหรืออัปเดตฐานข้อมูลทั้งหมด</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ครั้งแรกที่ติดตั้ง และทุกครั้งที่อัปเดตเป็นรุ่นที่มีตารางเพิ่ม</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทำที่ Supabase &gt; SQL Editor · คัดลอกทั้งไฟล์ · รันซ้ำได้ ไม่ลบข้อมูลเดิม · ต้องดูตารางสรุปท้ายผล</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">select * from ชื่อตาราง limit 20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ดูข้อมูลในตารางตรง ๆ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตอนไล่หาสาเหตุว่าข้อมูลเข้าไปจริงหรือไม่</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทำที่ Supabase &gt; SQL Editor · อ่านอย่างเดียว ปลอดภัย</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">notify pgrst, 'reload schema'</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="2">
+      <c r="B28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">สั่งให้ API รู้จักตารางที่เพิ่งสร้าง</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr" s="2">
+      <c r="C28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">เมื่อขึ้น error PGRST205 ว่าหาตารางไม่เจอ</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr" s="2">
+      <c r="D28" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">อยู่ท้าย schema.sql อยู่แล้ว สั่งแยกเมื่อจำเป็นเท่านั้น</t>
         </is>

--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -2960,185 +2960,202 @@
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">หน้าล็อกอินขึ้นกล่องเหลือง ยังไม่ได้ตั้งค่า Supabase</t>
+          <t xml:space="preserve">ติดตั้งแล้วแต่ใช้ไม่ได้ และยังไม่รู้ว่าพลาดตรงไหน</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตัวแปรไม่ถึงหน้าเว็บ</t>
+          <t xml:space="preserve">ยังไม่ได้ตรวจว่าตอนนี้ติดตั้งถึงขั้นไหน</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ใส่ค่าที่ Vercel แล้วกด Redeploy · ตรวจว่าชื่อสะกดตรงเป๊ะรวมคำว่า NEXT_PUBLIC_ และติ๊กครบทั้งสาม environment</t>
+          <t xml:space="preserve">สั่ง npm run setup ก่อนเป็นอย่างแรก · มันตรวจของจริงถึง Supabase แล้วบอกเป็นข้อ ๆ ว่าเหลืออะไร · ส่วนใหญ่จบที่ขั้นนี้</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อีเมลหรือรหัสผ่านไม่ถูกต้อง</t>
+          <t xml:space="preserve">หน้าล็อกอินขึ้นกล่องเหลือง ยังไม่ได้ตั้งค่า Supabase</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค่าที่ส่งไปไม่ตรงกับที่ Supabase มี</t>
+          <t xml:space="preserve">ตัวแปรไม่ถึงหน้าเว็บ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจว่าผู้ใช้มีจริงที่ Authentication &gt; Users · ถ้าไม่แน่ใจรหัสผ่าน ให้กด Reset password ตั้งใหม่</t>
+          <t xml:space="preserve">ใส่ค่าที่ Vercel แล้วกด Redeploy · ตรวจว่าชื่อสะกดตรงเป๊ะรวมคำว่า NEXT_PUBLIC_ และติ๊กครบทั้งสาม environment</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">อีเมลนี้ยังไม่ได้ยืนยัน</t>
+          <t xml:space="preserve">อีเมลหรือรหัสผ่านไม่ถูกต้อง</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ลืมติ๊ก Auto Confirm User ตอนสร้างผู้ใช้</t>
+          <t xml:space="preserve">ค่าที่ส่งไปไม่ตรงกับที่ Supabase มี</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Authentication &gt; Users &gt; กดที่ผู้ใช้ &gt; Confirm email</t>
+          <t xml:space="preserve">ตรวจว่าผู้ใช้มีจริงที่ Authentication &gt; Users · ถ้าไม่แน่ใจรหัสผ่าน ให้กด Reset password ตั้งใหม่</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ไม่มีสิทธิ์เข้าถึง ตรวจสอบ anon key</t>
+          <t xml:space="preserve">อีเมลนี้ยังไม่ได้ยืนยัน</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">anon key ผิด หรือเป็นของโปรเจกต์อื่น</t>
+          <t xml:space="preserve">ลืมติ๊ก Auto Confirm User ตอนสร้างผู้ใช้</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คัดลอก anon public key ใหม่จาก Project Settings &gt; API แล้ว Redeploy</t>
+          <t xml:space="preserve">Authentication &gt; Users &gt; กดที่ผู้ใช้ &gt; Confirm email</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">พยายามเข้าสู่ระบบบ่อยเกินไป</t>
+          <t xml:space="preserve">ไม่มีสิทธิ์เข้าถึง ตรวจสอบ anon key</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Supabase จำกัดอัตราการล็อกอิน</t>
+          <t xml:space="preserve">anon key ผิด หรือเป็นของโปรเจกต์อื่น</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รอสักครู่แล้วลองใหม่ · ไม่ต้องแก้อะไร</t>
+          <t xml:space="preserve">คัดลอก anon public key ใหม่จาก Project Settings &gt; API แล้ว Redeploy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ล็อกอินผ่าน แต่หน้าจอขึ้นว่ายังใช้งานไม่ได้ และบอกชื่อตาราง</t>
+          <t xml:space="preserve">พยายามเข้าสู่ระบบบ่อยเกินไป</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ยังไม่ได้รัน schema.sql หรือรันไม่จบ</t>
+          <t xml:space="preserve">Supabase จำกัดอัตราการล็อกอิน</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รัน supabase/schema.sql ทั้งไฟล์อีกครั้ง แล้วดูตารางสรุปให้ขึ้น ผ่าน ครบทุกแถว</t>
+          <t xml:space="preserve">รอสักครู่แล้วลองใหม่ · ไม่ต้องแก้อะไร</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกไม่ได้ ขึ้น 42501 permission denied for sequence</t>
+          <t xml:space="preserve">ล็อกอินผ่าน แต่หน้าจอขึ้นว่ายังใช้งานไม่ได้ และบอกชื่อตาราง</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สิทธิ์ของ sequence ยังไม่ได้ให้ (คนละเรื่องกับสิทธิ์ของตาราง)</t>
+          <t xml:space="preserve">ยังไม่ได้รัน schema.sql หรือรันไม่จบ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รัน supabase/schema.sql ทั้งไฟล์อีกครั้ง ส่วนที่ให้สิทธิ์ sequence อยู่ท้ายไฟล์</t>
+          <t xml:space="preserve">รัน supabase/schema.sql ทั้งไฟล์อีกครั้ง แล้วดูตารางสรุปให้ขึ้น ผ่าน ครบทุกแถว</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">บันทึกไม่ได้ ขึ้น 42501 permission denied for table</t>
+          <t xml:space="preserve">บันทึกไม่ได้ ขึ้น 42501 permission denied for sequence</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">role authenticated ยังไม่ได้รับ GRANT บนตารางนั้น</t>
+          <t xml:space="preserve">สิทธิ์ของ sequence ยังไม่ได้ให้ (คนละเรื่องกับสิทธิ์ของตาราง)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รัน supabase/schema.sql ทั้งไฟล์อีกครั้ง</t>
+          <t xml:space="preserve">รัน supabase/schema.sql ทั้งไฟล์อีกครั้ง ส่วนที่ให้สิทธิ์ sequence อยู่ท้ายไฟล์</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เปิดเว็บแล้วขึ้น Failed to fetch</t>
+          <t xml:space="preserve">บันทึกไม่ได้ ขึ้น 42501 permission denied for table</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Project URL ผิด หรือโปรเจกต์ Supabase ถูกหยุด</t>
+          <t xml:space="preserve">role authenticated ยังไม่ได้รับ GRANT บนตารางนั้น</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ตรวจ URL ให้ตรง · โปรเจกต์ฟรีที่ไม่มีคนใช้เกิน 7 วันจะถูก pause ให้เข้า Dashboard กด Restore</t>
+          <t xml:space="preserve">รัน supabase/schema.sql ทั้งไฟล์อีกครั้ง</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">แก้โค้ดแล้วแต่หน้าเว็บยังเป็นของเดิม</t>
+          <t xml:space="preserve">เปิดเว็บแล้วขึ้น Failed to fetch</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เบราว์เซอร์ถือไฟล์เก่า หรือ Vercel ยัง deploy ไม่เสร็จ</t>
+          <t xml:space="preserve">Project URL ผิด หรือโปรเจกต์ Supabase ถูกหยุด</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดูเลขรุ่นท้ายเมนูซ้ายว่าตรงกับ APP_BUILD หรือยัง · ถ้าตรงแล้วให้กด Ctrl+F5 ล้างแคช</t>
+          <t xml:space="preserve">ตรวจ URL ให้ตรง · โปรเจกต์ฟรีที่ไม่มีคนใช้เกิน 7 วันจะถูก pause ให้เข้า Dashboard กด Restore</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">แก้โค้ดแล้วแต่หน้าเว็บยังเป็นของเดิม</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เบราว์เซอร์ถือไฟล์เก่า หรือ Vercel ยัง deploy ไม่เสร็จ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ดูเลขรุ่นท้ายเมนูซ้ายว่าตรงกับ APP_BUILD หรือยัง · ถ้าตรงแล้วให้กด Ctrl+F5 ล้างแคช</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">ไม่รู้ว่าพลาดตรงไหน</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr" s="2">
+      <c r="B13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ต้องดูของจริงที่ฝั่งเบราว์เซอร์</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr" s="2">
+      <c r="C13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">กด F12 &gt; แท็บ Network &gt; ลองล็อกอิน &gt; ดูคำขอ token?grant_type=password · ไม่มีคำขอ = ตัวแปรไม่ถึงหน้าเว็บ · 400 = รหัสผ่านไม่ตรง · 401 = anon key ผิด</t>
         </is>

--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -10,6 +10,7 @@
     <sheet name="6 แก้ปัญหา" sheetId="6" r:id="rId6"/>
     <sheet name="7 คำสั่งที่ต้องใช้" sheetId="7" r:id="rId7"/>
     <sheet name="8 ความปลอดภัย" sheetId="8" r:id="rId8"/>
+    <sheet name="9 ผังลำดับงาน" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -137,7 +138,7 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 วิธีใช้ · 2 เช็คลิสต์ติดตั้ง · 3 ค่าที่ต้องตั้ง · 4 ตั้งค่าเริ่มต้นเชิงพาณิชย์ · 5 ตรวจรับก่อนใช้จริง · 6 แก้ปัญหา · 7 คำสั่งที่ต้องใช้ · 8 ความปลอดภัย</t>
+          <t xml:space="preserve">1 วิธีใช้ · 2 เช็คลิสต์ติดตั้ง · 3 ค่าที่ต้องตั้ง · 4 ตั้งค่าเริ่มต้นเชิงพาณิชย์ · 5 ตรวจรับก่อนใช้จริง · 6 แก้ปัญหา · 7 คำสั่งที่ต้องใช้ · 8 ความปลอดภัย · 9 ผังลำดับงาน</t>
         </is>
       </c>
     </row>
@@ -157,107 +158,119 @@
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คำสั่งเดียวที่ควรจำ</t>
+          <t xml:space="preserve">อยากเห็นภาพรวมก่อน</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">npm run setup — ตรวจให้ว่าติดตั้งถึงไหนแล้ว และบอกเป็นข้อ ๆ ว่าเหลืออะไรต้องทำ · สั่งได้ตลอดทุกขั้น</t>
+          <t xml:space="preserve">ดูชีต 9 ผังลำดับงาน — บอกว่าแต่ละขั้นส่งอะไรต่อให้ขั้นถัดไป จึงเห็นว่าทำไมต้องเรียงแบบนี้ · ฉบับรูปวาดอยู่ในไฟล์ Docs/คู่มือการติดตั้ง.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ค่าที่จำเป็นจริง ๆ มีแค่</t>
+          <t xml:space="preserve">คำสั่งเดียวที่ควรจำ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEXT_PUBLIC_SUPABASE_URL และ NEXT_PUBLIC_SUPABASE_ANON_KEY — ที่เหลือเป็นของเสริมทั้งหมด</t>
+          <t xml:space="preserve">npm run setup — ตรวจให้ว่าติดตั้งถึงไหนแล้ว และบอกเป็นข้อ ๆ ว่าเหลืออะไรต้องทำ · สั่งได้ตลอดทุกขั้น</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">ค่าที่จำเป็นจริง ๆ มีแค่</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">NEXT_PUBLIC_SUPABASE_URL และ NEXT_PUBLIC_SUPABASE_ANON_KEY — ที่เหลือเป็นของเสริมทั้งหมด</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สามข้อที่พลาดบ่อยที่สุด</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr" s="2">
+      <c r="B13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1 ลืมติ๊ก Auto Confirm User · 2 ใส่ตัวแปรแล้วไม่ได้ Redeploy · 3 รัน schema.sql ไม่จบแล้วไม่ได้ดูตารางสรุป</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">จำนวนตารางฐานข้อมูล</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">44 ตาราง — สร้างครบจากไฟล์ supabase/schema.sql ไฟล์เดียว</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">จำนวนหน้าจอ</t>
+          <t xml:space="preserve">จำนวนตารางฐานข้อมูล</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">56 หน้า</t>
+          <t xml:space="preserve">44 ตาราง — สร้างครบจากไฟล์ supabase/schema.sql ไฟล์เดียว</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">รุ่นของโปรแกรมตอนสร้างไฟล์นี้</t>
+          <t xml:space="preserve">จำนวนหน้าจอ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFAU 3.3 · รอบ 94 (2026-09-12)</t>
+          <t xml:space="preserve">56 หน้า</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">สร้างไฟล์นี้เมื่อ</t>
+          <t xml:space="preserve">รุ่นของโปรแกรมตอนสร้างไฟล์นี้</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">OFAU 3.3 · รอบ 96 (2026-09-12)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">คู่มือฉบับเต็ม</t>
+          <t xml:space="preserve">สร้างไฟล์นี้เมื่อ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Docs/คู่มือการติดตั้ง.md (อธิบายเหตุผลและวิธีแก้ปัญหาแบบละเอียด)</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">คู่มือฉบับเต็ม</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Docs/คู่มือการติดตั้ง.md (อธิบายเหตุผลและวิธีแก้ปัญหาแบบละเอียด)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">สร้างไฟล์นี้ใหม่</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr" s="2">
+      <c r="B20" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">node tools/make-setup-xlsx.mjs</t>
         </is>
@@ -1547,7 +1560,7 @@
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 94 (2026-09-12))</t>
+          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 96 (2026-09-12))</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="2">
@@ -4564,4 +4577,906 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="6" width="76" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>ผัง</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t>ลำดับ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t>จุด / ขั้นตอน</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t>ทำอะไรที่ขั้นนี้</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>ได้อะไรส่งต่อให้ขั้นถัดไป</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>ถ้าข้ามหรือทำผิดลำดับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A. ระบบประกอบด้วยอะไร</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผู้ใช้ (เบราว์เซอร์)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปิดเว็บตามที่อยู่ของ Vercel</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">คำขอเปิดหน้าเว็บ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ถ้าเปิดไม่ขึ้นเลย ปัญหาอยู่ที่ Vercel ไม่ใช่ที่ฐานข้อมูล</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A. ระบบประกอบด้วยอะไร</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Vercel (ที่รันเว็บ)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เอาโค้ดจาก GitHub มารัน · เก็บเฉพาะโค้ด ไม่มีข้อมูลของกิจการอยู่เลย</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หน้าเว็บ พร้อมค่า URL และ anon key ที่ฝังไว้ตอน build</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">deploy ใหม่กี่ครั้งข้อมูลก็ไม่หาย เพราะข้อมูลไม่ได้อยู่ที่นี่</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">A. ระบบประกอบด้วยอะไร</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Supabase (ฐานข้อมูล + ล็อกอิน)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เก็บข้อมูลจริงทั้งหมด และตรวจอีเมลกับรหัสผ่านตอนล็อกอิน</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อมูลที่หน้าเว็บขอ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลบโปรเจกต์ Supabase เมื่อไร ข้อมูลหายทั้งหมดทันที ไม่มีที่สำรองอัตโนมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">B. ลำดับการติดตั้ง</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เตรียมโค้ด</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">git clone มาเป็นโปรเจกต์ใหม่</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">โฟลเดอร์โปรเจกต์ที่มีไฟล์ครบ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ขาด jsconfig.json แล้ว build ไม่ผ่านทุกครั้ง</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">B. ลำดับการติดตั้ง</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Supabase</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างโปรเจกต์ · รัน schema.sql · สร้างผู้ใช้คนแรก (ติ๊ก Auto Confirm User)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Project URL และ anon public key  &lt;- ขั้นถัดไปต้องใช้สองค่านี้</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทำ Vercel ก่อนขั้นนี้จะไม่มีค่าจะใส่ · นี่คือเหตุผลที่ Supabase ต้องมาก่อน</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">B. ลำดับการติดตั้ง</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GitHub</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">push โค้ดขึ้น repo (ตั้งเป็น Private ถ้าเป็นงานของกิจการ)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ที่อยู่ repo ให้ Vercel ไปอ่าน</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Vercel อ่านโค้ดจาก GitHub ไม่ได้อัปโหลดไฟล์ตรง</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">B. ลำดับการติดตั้ง</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Vercel</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างโปรเจกต์จาก repo · ใส่ค่าสองตัวจากขั้น 2 · Redeploy หนึ่งครั้ง</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เว็บที่ใช้งานได้จริง</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใส่ค่าแล้วไม่ Redeploy ค่าใหม่จะไม่มีผล เพราะค่าถูกฝังตอน build</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">B. ลำดับการติดตั้ง</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปิดเว็บและล็อกอิน</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ล็อกอินด้วยผู้ใช้ที่สร้างไว้ในขั้น 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยืนยันว่าทั้งสามส่วนต่อกันติดแล้ว</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ล็อกอินไม่ได้ ให้สั่ง npm run setup ก่อนเป็นอย่างแรก</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">C. ค่าสองตัวไปไหนบ้าง</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ต้นทาง: Supabase &gt; Settings &gt; API</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">คัดลอก Project URL และ anon public key</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ค่าสองตัวที่ต้องใส่สองที่</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">อย่าหยิบ service_role มาใส่แทน anon key เด็ดขาด</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">C. ค่าสองตัวไปไหนบ้าง</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปลายทางที่ 1: ไฟล์ .env.local</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใส่ในเครื่องตัวเอง ใช้ตอนสั่ง npm run dev</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เว็บในเครื่องใช้งานได้</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไฟล์นี้ต้องไม่ขึ้น git เด็ดขาด</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">C. ค่าสองตัวไปไหนบ้าง</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ปลายทางที่ 2: Vercel &gt; Environment Variables</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใส่ค่าเดียวกัน ติ๊กครบทั้งสาม environment</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เว็บจริงใช้งานได้</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใส่ที่เครื่องอย่างเดียว เว็บจริงจะยังล็อกอินไม่ได้ · npm run setup ตรวจฝั่งนี้ให้ไม่ได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">C. ค่าสองตัวไปไหนบ้าง</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Redeploy หนึ่งครั้ง</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สั่งที่ Vercel &gt; Deployments</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ค่าถูกฝังลงไฟล์ที่เบราว์เซอร์โหลด</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อนี้ลืมกันบ่อยที่สุดเป็นอันดับสอง รองจากลืมติ๊ก Auto Confirm User</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายเอกสาร)</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อมูลกิจการ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ชื่อ ที่อยู่ เลขประจำตัวผู้เสียภาษี สาขา</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หัวเอกสารที่ถูกต้องตามกฎหมาย</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ออกเอกสารก่อนตั้งค่านี้ เอกสารจะใช้ไม่ได้ตามกฎหมาย</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายเอกสาร)</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กลุ่มเอกสาร</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รูปแบบเลขที่ เช่น IV-202609-0001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เลขที่เอกสารที่ออกให้เองทุกใบ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปลี่ยนทีหลังแล้วเลขเก่าไม่เปลี่ยนตาม จะได้เอกสารสองรูปแบบปนกัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายสินค้า)</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">คลังและที่เก็บ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เพิ่มคลัง แล้วเพิ่มช่องเก็บในแต่ละคลัง</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ที่ให้ของไปอยู่</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไม่มีคลัง รับสินค้าเข้าไม่ได้เลย</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายสินค้า)</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">กลุ่ม ยี่ห้อ ประเภทสินค้า</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนสามมิติสำหรับจำแนกสินค้า</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รายการให้เลือกตอนเพิ่มสินค้า</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไม่ตั้งก่อน จะต้องพิมพ์เอง แล้วชื่อสะกดต่างกันทีละนิดจนเป้าขายจับคู่ไม่ติด</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายสินค้า)</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อมูลสินค้า</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รหัส ชื่อ หน่วยนับ ราคา บาร์โค๊ด (หรือนำเข้าจาก Excel ถ้ามีเยอะ)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">แกนของทั้งระบบ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไม่มีสินค้า ทำอะไรต่อไม่ได้เลย</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายสินค้า)</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยอดยกมา</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รับสินค้าเข้าครั้งแรก หรือใช้ใบตรวจนับ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยอดคงเหลือตั้งต้นที่ตรงกับของจริง</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไม่ใส่ ระบบคิดว่าไม่มีของเลย แล้วขายไม่ได้เพราะสต็อกไม่พอ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายคู่ค้า)</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ทะเบียนลูกค้าและเจ้าหนี้</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รหัส ชื่อ ที่อยู่แยกช่อง เลขผู้เสียภาษี</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อมูลผู้ซื้อผู้ขายบนเอกสาร</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใบกำกับภาษีต้องมีที่อยู่ผู้ซื้อครบ ไม่งั้นลูกค้าตีเอกสารกลับ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายคู่ค้า)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">พนักงานขาย</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รหัสและชื่อพนักงานขายทุกคน</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผูกกับใบขายเพื่อดูยอดรายคน</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตั้งทีหลังก็ได้ ไม่บล็อกงาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายผู้ใช้)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ผู้ใช้งานที่เหลือ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บัญชีเข้าระบบรายคน</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ใช้บัญชีร่วมกันแล้วตรวจสอบย้อนหลังไม่ได้ว่าใครทำอะไร</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">D. ตั้งค่าในโปรแกรม (สายผู้ใช้)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สิทธิการใช้งานรายคน</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เลือกผู้ใช้ทีละคน แล้วติ๊กว่าเห็นหน้าจอไหนและแก้ไขได้ไหม</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">พนักงานเห็นเฉพาะงานของตัวเอง</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เป็นการคุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล (ดูชีต 8 ความปลอดภัย)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">E. ตรวจรับก่อนเปิดใช้จริง</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ซื้อ 1 ใบ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">บันทึกใบซื้อทดลอง</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ของเข้าคลังและยอดคงเหลือเพิ่ม</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยอดไม่เพิ่ม แปลว่าคลังหรือช่องเก็บยังไม่ถูก</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">E. ตรวจรับก่อนเปิดใช้จริง</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตรวจยอดคงเหลือ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เปิดหน้าข้อมูลสินค้าดูรายคลังรายช่องเก็บ</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยืนยันว่าของเข้าถูกที่</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">E. ตรวจรับก่อนเปิดใช้จริง</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ขาย POS 1 บิล</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยิงบาร์โค๊ด คิดเงิน พิมพ์ใบเสร็จ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยอดคงเหลือลดลงตามจริง</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">E. ตรวจรับก่อนเปิดใช้จริง</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>4</v>
+      </c>
+      <c r="C27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ออกใบกำกับภาษี 1 ใบ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ตรวจหัวเอกสารว่าชื่อกิจการและเลขผู้เสียภาษีถูก</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เอกสารที่ใช้ได้จริง</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">หัวเอกสารผิด แปลว่ายังไม่ได้ตั้งข้อมูลกิจการ (ผัง D ขั้น 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">E. ตรวจรับก่อนเปิดใช้จริง</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ดูรายงานว่ายอดตรง</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">เทียบกับที่ทดลองทำไปทุกใบ</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ยืนยันว่าตัวเลขเชื่อได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">E. ตรวจรับก่อนเปิดใช้จริง</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">สำรองข้อมูล แล้วทดลองกู้คืน</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ดาวน์โหลดไฟล์ แล้วกู้คืนกลับจริง ๆ</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">รู้ว่ากู้คืนได้จริง</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ข้อนี้ห้ามข้าม ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง และจะรู้ตอนที่สายเกินไป</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">E. ตรวจรับก่อนเปิดใช้จริง</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ล้างข้อมูลทดลอง แล้วใส่ยอดจริง</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ลบเอกสารทดลองทั้งหมด</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">พร้อมเปิดใช้งานจริง</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ไม่ล้าง รายงานเดือนแรกจะมีตัวเลขทดลองปน</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -11,6 +11,7 @@
     <sheet name="7 คำสั่งที่ต้องใช้" sheetId="7" r:id="rId7"/>
     <sheet name="8 ความปลอดภัย" sheetId="8" r:id="rId8"/>
     <sheet name="9 ผังลำดับงาน" sheetId="9" r:id="rId9"/>
+    <sheet name="10 ผังแบบรูป" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -51,8 +52,2549 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="133350"/>
+    <xdr:ext cx="10858500" cy="285750"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="รูป 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ผังลำดับงานการติดตั้ง — รายละเอียดของแต่ละขั้นอยู่ที่ชีต 9 ผังลำดับงาน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="571500"/>
+    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="รูป 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="8A978F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>A. ระบบประกอบด้วยอะไร</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="876300"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="รูป 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ผู้ใช้ (เบราว์เซอร์)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1819275" y="1428750"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="รูป 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8A978F"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="1733550"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="รูป 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel — ที่รันเว็บ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บเฉพาะโค้ด</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1819275" y="2286000"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="รูป 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8A978F"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="2590800"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="รูป 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Supabase — ฐานข้อมูล + ล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ข้อมูลจริงอยู่ที่นี่ที่เดียว</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="3524250"/>
+    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="รูป 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>B. ลำดับการติดตั้ง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="3829050"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="รูป 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>1. เตรียมโค้ด (git clone)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1819275" y="4381500"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="รูป 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="4686300"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="รูป 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>2. Supabase</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>รัน schema.sql + สร้างผู้ใช้คนแรก</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1819275" y="5238750"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="รูป 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="5543550"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="รูป 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>3. GitHub (push โค้ดขึ้น repo)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1819275" y="6096000"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="รูป 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="6400800"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="รูป 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>4. Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ค่า 2 ตัว แล้ว Redeploy</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="1819275" y="6953250"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="รูป 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="7258050"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="รูป 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>5. เปิดเว็บ ล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="571500"/>
+    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="รูป 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B26A00"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>C. ค่าสองตัวไปไหนบ้าง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="876300"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="รูป 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Supabase &gt; Settings &gt; API</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>คัดลอก URL + anon key</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="1428750"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="รูป 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="B26A00"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="1733550"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="รูป 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>.env.local</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใช้ตอนรันในเครื่อง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="2286000"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="รูป 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="B26A00"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="2590800"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="รูป 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel &gt; Environment Variables</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใช้ตอนรันบนเว็บจริง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="3143250"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="รูป 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="B26A00"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="3448050"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="รูป 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Redeploy หนึ่งครั้ง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ค่าถูกฝังตอน build</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="4381500"/>
+    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="รูป 27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>E. ตรวจรับก่อนเปิดใช้จริง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="4686300"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="รูป 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>1. ซื้อ 1 ใบ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="5238750"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="รูป 29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="5543550"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="รูป 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>2. ตรวจยอดคงเหลือ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="6096000"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="รูป 31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="6400800"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="รูป 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>3. ขาย POS 1 บิล</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="6953250"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="รูป 33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="7258050"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="รูป 34"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>4. ออกใบกำกับภาษี 1 ใบ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="7810500"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="รูป 35"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="8115300"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="รูป 36"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>5. ดูรายงานว่ายอดตรง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="8667750"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="รูป 37"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="8972550"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="รูป 38"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>6. สำรอง แล้วทดลองกู้คืน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="5629275" y="9525000"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="รูป 39"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4095750" y="9829800"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="รูป 40"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>7. ล้างข้อมูลทดลอง ใส่ยอดจริง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="571500"/>
+    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="รูป 41"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>D. ตั้งค่าในโปรแกรม</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="876300"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="รูป 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>1. ข้อมูลกิจการ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="1428750"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="รูป 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="1733550"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="รูป 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>2. กลุ่มเอกสาร (รูปแบบเลขที่)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="2286000"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="รูป 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="2590800"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="รูป 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>3. คลังและที่เก็บ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="3143250"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="รูป 47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="3448050"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="รูป 48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>4. กลุ่ม ยี่ห้อ ประเภทสินค้า</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="4000500"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="รูป 49"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="4305300"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="รูป 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>5. ข้อมูลสินค้า</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="4857750"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="รูป 51"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="5162550"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="รูป 52"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>6. ยอดยกมา</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="5715000"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="รูป 53"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="6019800"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="รูป 54"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>7. ทะเบียนลูกค้าและเจ้าหนี้</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="6572250"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="รูป 55"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="6877050"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="รูป 56"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>8. พนักงานขาย</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="7429500"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="57" name="รูป 57"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="7734300"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="รูป 58"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>9. ผู้ใช้งานที่เหลือ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9439275" y="8286750"/>
+    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="59" name="รูป 59"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7905750" y="8591550"/>
+    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="60" name="รูป 60"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>10. สิทธิการใช้งานรายคน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="10553700"/>
+    <xdr:ext cx="10858500" cy="495300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="รูป 61"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>จำสองข้อนี้: Supabase ต้องมาก่อน Vercel เพราะขั้น Vercel ต้องใช้ค่าที่ได้จาก Supabase  ·  ใส่ค่าที่ Vercel แล้วต้อง Redeploy หนึ่งครั้ง ค่าใหม่ถึงจะมีผล</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
@@ -138,7 +2680,7 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1 วิธีใช้ · 2 เช็คลิสต์ติดตั้ง · 3 ค่าที่ต้องตั้ง · 4 ตั้งค่าเริ่มต้นเชิงพาณิชย์ · 5 ตรวจรับก่อนใช้จริง · 6 แก้ปัญหา · 7 คำสั่งที่ต้องใช้ · 8 ความปลอดภัย · 9 ผังลำดับงาน</t>
+          <t xml:space="preserve">1 วิธีใช้ · 2 เช็คลิสต์ติดตั้ง · 3 ค่าที่ต้องตั้ง · 4 ตั้งค่าเริ่มต้นเชิงพาณิชย์ · 5 ตรวจรับก่อนใช้จริง · 6 แก้ปัญหา · 7 คำสั่งที่ต้องใช้ · 8 ความปลอดภัย · 9 ผังลำดับงาน · 10 ผังแบบรูป</t>
         </is>
       </c>
     </row>
@@ -163,7 +2705,7 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ดูชีต 9 ผังลำดับงาน — บอกว่าแต่ละขั้นส่งอะไรต่อให้ขั้นถัดไป จึงเห็นว่าทำไมต้องเรียงแบบนี้ · ฉบับรูปวาดอยู่ในไฟล์ Docs/คู่มือการติดตั้ง.md</t>
+          <t xml:space="preserve">ดูชีต 10 ผังแบบรูป ก่อน แล้วค่อยดูชีต 9 ที่บอกว่าแต่ละขั้นส่งอะไรต่อให้ขั้นถัดไป · ฉบับรูปวาดอยู่ในไฟล์ Docs/คู่มือการติดตั้ง.md</t>
         </is>
       </c>
     </row>
@@ -236,7 +2778,7 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFAU 3.3 · รอบ 96 (2026-09-12)</t>
+          <t xml:space="preserve">OFAU 3.3 · รอบ 97 (2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -280,8 +2822,17 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetData>
+    <row r="1"/>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1560,7 +4111,7 @@
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 96 (2026-09-12))</t>
+          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 97 (2026-09-12))</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="2">
@@ -1579,7 +4130,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1934,7 +4485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -2569,7 +5120,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -2946,7 +5497,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -3179,7 +5730,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="64" customWidth="1"/>
@@ -3738,7 +6289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -4580,7 +7131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>

--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -55,8 +55,8 @@
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="133350"/>
-    <xdr:ext cx="10858500" cy="285750"/>
+    <xdr:pos x="285750" y="114300"/>
+    <xdr:ext cx="13049250" cy="438150"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="รูป 2"/>
@@ -81,14 +81,27 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1400" b="1">
+            <a:rPr lang="th-TH" sz="1600" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ผังลำดับงานการติดตั้ง — รายละเอียดของแต่ละขั้นอยู่ที่ชีต 9 ผังลำดับงาน</a:t>
+            <a:t>ผังลำดับงานการติดตั้ง One for All Ultra</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>อ่านจากบนลงล่างทีละคอลัมน์ · บรรทัดล่างสุดของแต่ละกล่องคือผลที่ได้ ถ้าเป็นตัวหนาสีแดงคือข้อที่พลาดบ่อย</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -96,11 +109,56 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="571500"/>
-    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:pos x="285750" y="590550"/>
+    <xdr:ext cx="13049250" cy="323850"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="รูป 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>จำสองข้อนี้ก่อน:  Supabase ต้องมาก่อน Vercel เพราะขั้น Vercel ต้องใช้ค่าที่ได้จาก Supabase   ·   ใส่ค่าที่ Vercel แล้วต้อง Redeploy หนึ่งครั้ง ค่าใหม่ถึงจะมีผล</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="1066800"/>
+    <xdr:ext cx="4095750" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="รูป 4"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -122,7 +180,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1100" b="1">
+            <a:rPr lang="th-TH" sz="1200" b="1">
               <a:solidFill>
                 <a:srgbClr val="8A978F"/>
               </a:solidFill>
@@ -130,6 +188,19 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>A. ระบบประกอบด้วยอะไร</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>สามส่วนนี้อยู่คนละที่ ไม่ได้อยู่เครื่องเดียวกัน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -137,11 +208,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="876300"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="285750" y="1504950"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="รูป 4"/>
+        <xdr:cNvPr id="5" name="รูป 5"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -167,14 +238,40 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="3A423D"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ผู้ใช้ (เบราว์เซอร์)</a:t>
+            <a:t>ผู้ใช้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เปิดเว็บผ่านเบราว์เซอร์ ที่อยู่ของ Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: หน้าเว็บของระบบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -182,11 +279,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="1819275" y="1428750"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="2238375" y="2419350"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="รูป 5"/>
+        <xdr:cNvPr id="6" name="รูป 6"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -217,11 +314,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="1733550"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="285750" y="2667000"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="รูป 6"/>
+        <xdr:cNvPr id="7" name="รูป 7"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -247,7 +344,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="3A423D"/>
               </a:solidFill>
@@ -260,14 +357,27 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="900">
               <a:solidFill>
                 <a:srgbClr val="3A423D"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เก็บเฉพาะโค้ด</a:t>
+            <a:t>เอาโค้ดจาก GitHub มารันเอง ทุกครั้งที่ push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บเฉพาะโค้ด ไม่มีข้อมูลของกิจการอยู่เลย</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -275,11 +385,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="1819275" y="2286000"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="2238375" y="3581400"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="รูป 7"/>
+        <xdr:cNvPr id="8" name="รูป 8"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -310,11 +420,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="2590800"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="285750" y="3829050"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="รูป 8"/>
+        <xdr:cNvPr id="9" name="รูป 9"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -340,7 +450,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="3A423D"/>
               </a:solidFill>
@@ -353,14 +463,27 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="900">
               <a:solidFill>
                 <a:srgbClr val="3A423D"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ข้อมูลจริงอยู่ที่นี่ที่เดียว</a:t>
+            <a:t>เก็บข้อมูลจริงทั้งหมด และตรวจรหัสผ่านตอนล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบโปรเจกต์นี้เมื่อไร ข้อมูลหายทั้งหมดทันที</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -368,11 +491,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="3524250"/>
-    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:pos x="285750" y="5086350"/>
+    <xdr:ext cx="4095750" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="รูป 9"/>
+        <xdr:cNvPr id="10" name="รูป 10"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -394,7 +517,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1100" b="1">
+            <a:rPr lang="th-TH" sz="1200" b="1">
               <a:solidFill>
                 <a:srgbClr val="2E7D52"/>
               </a:solidFill>
@@ -402,6 +525,19 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>B. ลำดับการติดตั้ง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ห้าขั้น ข้ามลำดับไม่ได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -409,11 +545,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="3829050"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="285750" y="5524500"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="รูป 10"/>
+        <xdr:cNvPr id="11" name="รูป 11"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -439,14 +575,40 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>1. เตรียมโค้ด (git clone)</a:t>
+            <a:t>1. เตรียมโค้ด</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>git clone มาเป็นโปรเจกต์ใหม่</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: โฟลเดอร์ที่มีไฟล์ครบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -454,11 +616,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="1819275" y="4381500"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="2238375" y="6438900"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="รูป 11"/>
+        <xdr:cNvPr id="12" name="รูป 12"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -489,11 +651,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="4686300"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="285750" y="6686550"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="รูป 12"/>
+        <xdr:cNvPr id="13" name="รูป 13"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -519,7 +681,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -532,14 +694,27 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="900">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รัน schema.sql + สร้างผู้ใช้คนแรก</a:t>
+            <a:t>สร้างโปรเจกต์ (Region สิงคโปร์) · รัน schema.sql ทั้งไฟล์ · สร้างผู้ใช้คนแรก</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ตอนสร้างผู้ใช้ ต้องติ๊ก Auto Confirm User</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -547,11 +722,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="1819275" y="5238750"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="2238375" y="7600950"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="รูป 13"/>
+        <xdr:cNvPr id="14" name="รูป 14"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -582,11 +757,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="5543550"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="285750" y="7848600"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="รูป 14"/>
+        <xdr:cNvPr id="15" name="รูป 15"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -612,14 +787,40 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. GitHub (push โค้ดขึ้น repo)</a:t>
+            <a:t>3. GitHub</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>สร้าง repo (ตั้ง Private) แล้ว push โค้ดขึ้นไป</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ที่อยู่ repo ให้ Vercel ไปอ่าน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -627,11 +828,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="1819275" y="6096000"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="2238375" y="8763000"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="รูป 15"/>
+        <xdr:cNvPr id="16" name="รูป 16"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -662,11 +863,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="6400800"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="285750" y="9010650"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="รูป 16"/>
+        <xdr:cNvPr id="17" name="รูป 17"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -692,7 +893,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -705,14 +906,27 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="900">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ใส่ค่า 2 ตัว แล้ว Redeploy</a:t>
+            <a:t>สร้างโปรเจกต์จาก repo · ใส่ค่าสองตัวจากขั้น 2 · ติ๊กครบ 3 environment</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ค่าแล้วต้อง Redeploy หนึ่งครั้ง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -720,11 +934,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="1819275" y="6953250"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="2238375" y="9925050"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="รูป 17"/>
+        <xdr:cNvPr id="18" name="รูป 18"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -755,11 +969,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="7258050"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="285750" y="10172700"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="รูป 18"/>
+        <xdr:cNvPr id="19" name="รูป 19"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -785,7 +999,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -793,6 +1007,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>5. เปิดเว็บ ล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใช้อีเมลและรหัสผ่านที่สร้างไว้ในขั้น 2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ล็อกอินไม่ได้ ให้สั่ง npm run setup ก่อน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -800,11 +1040,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="571500"/>
-    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:pos x="4762500" y="1066800"/>
+    <xdr:ext cx="4095750" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="รูป 19"/>
+        <xdr:cNvPr id="20" name="รูป 20"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -826,7 +1066,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1100" b="1">
+            <a:rPr lang="th-TH" sz="1200" b="1">
               <a:solidFill>
                 <a:srgbClr val="B26A00"/>
               </a:solidFill>
@@ -834,6 +1074,19 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>C. ค่าสองตัวไปไหนบ้าง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="8A5200"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ค่าเดียวกัน ต้องใส่สองที่</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -841,11 +1094,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="876300"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="1504950"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="รูป 20"/>
+        <xdr:cNvPr id="21" name="รูป 21"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -871,27 +1124,40 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Supabase &gt; Settings &gt; API</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:t>ต้นทาง: Supabase</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>คัดลอก URL + anon key</a:t>
+            <a:t>Project Settings &gt; API · คัดลอก Project URL และ anon public key</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ห้ามหยิบ service_role มาใส่แทน anon key</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -899,11 +1165,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="1428750"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="2419350"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="รูป 21"/>
+        <xdr:cNvPr id="22" name="รูป 22"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -934,11 +1200,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="1733550"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="2667000"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="รูป 22"/>
+        <xdr:cNvPr id="23" name="รูป 23"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -964,27 +1230,40 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>.env.local</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:t>ปลายทาง 1: .env.local</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ใช้ตอนรันในเครื่อง</a:t>
+            <a:t>ไฟล์ในเครื่องตัวเอง ใช้ตอนสั่ง npm run dev</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไฟล์นี้ต้องไม่ขึ้น git เด็ดขาด</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -992,11 +1271,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="2286000"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="3581400"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="รูป 23"/>
+        <xdr:cNvPr id="24" name="รูป 24"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1027,11 +1306,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="2590800"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="3829050"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="รูป 24"/>
+        <xdr:cNvPr id="25" name="รูป 25"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1057,27 +1336,40 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Vercel &gt; Environment Variables</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:t>ปลายทาง 2: Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ใช้ตอนรันบนเว็บจริง</a:t>
+            <a:t>Environment Variables · ติ๊กครบ Production, Preview, Development</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ที่เครื่องอย่างเดียว เว็บจริงยังล็อกอินไม่ได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1085,11 +1377,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="3143250"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="4743450"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="รูป 25"/>
+        <xdr:cNvPr id="26" name="รูป 26"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1120,11 +1412,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="3448050"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="4991100"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="รูป 26"/>
+        <xdr:cNvPr id="27" name="รูป 27"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1150,7 +1442,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
@@ -1163,14 +1455,27 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="900">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ค่าถูกฝังตอน build</a:t>
+            <a:t>Vercel &gt; Deployments &gt; Redeploy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="8A5200"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ค่าถูกฝังลงไฟล์ที่เบราว์เซอร์โหลด</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1178,11 +1483,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="4381500"/>
-    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:pos x="4762500" y="6248400"/>
+    <xdr:ext cx="4095750" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="รูป 27"/>
+        <xdr:cNvPr id="28" name="รูป 28"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1204,7 +1509,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1100" b="1">
+            <a:rPr lang="th-TH" sz="1200" b="1">
               <a:solidFill>
                 <a:srgbClr val="0B5FA5"/>
               </a:solidFill>
@@ -1212,6 +1517,19 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>E. ตรวจรับก่อนเปิดใช้จริง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เดินงานจริงหนึ่งรอบก่อนเสมอ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1219,11 +1537,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="4686300"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="6686550"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="รูป 28"/>
+        <xdr:cNvPr id="29" name="รูป 29"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1249,7 +1567,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="0A3358"/>
               </a:solidFill>
@@ -1257,6 +1575,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>1. ซื้อ 1 ใบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>บันทึกใบซื้อทดลองที่หน้าซื้อสินค้าและบริการ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ของเข้าคลัง ยอดคงเหลือเพิ่ม</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1264,11 +1608,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="5238750"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="7600950"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="รูป 29"/>
+        <xdr:cNvPr id="30" name="รูป 30"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1299,11 +1643,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="5543550"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="7848600"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="รูป 30"/>
+        <xdr:cNvPr id="31" name="รูป 31"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1329,7 +1673,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="0A3358"/>
               </a:solidFill>
@@ -1337,6 +1681,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>2. ตรวจยอดคงเหลือ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เปิดหน้าข้อมูลสินค้า ดูรายคลังรายช่องเก็บ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยืนยันว่าของเข้าถูกที่</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1344,11 +1714,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="6096000"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="8763000"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="รูป 31"/>
+        <xdr:cNvPr id="32" name="รูป 32"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1379,11 +1749,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="6400800"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="9010650"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="รูป 32"/>
+        <xdr:cNvPr id="33" name="รูป 33"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1409,7 +1779,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="0A3358"/>
               </a:solidFill>
@@ -1417,6 +1787,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>3. ขาย POS 1 บิล</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ยิงบาร์โค๊ด คิดเงิน พิมพ์ใบเสร็จ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยอดคงเหลือลดลงตามจริง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1424,11 +1820,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="6953250"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="9925050"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="รูป 33"/>
+        <xdr:cNvPr id="34" name="รูป 34"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1459,11 +1855,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="7258050"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="10172700"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="รูป 34"/>
+        <xdr:cNvPr id="35" name="รูป 35"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1489,7 +1885,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="0A3358"/>
               </a:solidFill>
@@ -1497,6 +1893,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>4. ออกใบกำกับภาษี 1 ใบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ตรวจหัวเอกสารว่าชื่อกิจการและเลขผู้เสียภาษีถูก</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หัวเอกสารผิด = ยังไม่ได้ตั้งข้อมูลกิจการ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1504,11 +1926,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="7810500"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="11087100"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="รูป 35"/>
+        <xdr:cNvPr id="36" name="รูป 36"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1539,11 +1961,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="8115300"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="11334750"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="รูป 36"/>
+        <xdr:cNvPr id="37" name="รูป 37"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1569,7 +1991,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="0A3358"/>
               </a:solidFill>
@@ -1577,6 +1999,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>5. ดูรายงานว่ายอดตรง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เทียบกับที่ทดลองทำไปทุกใบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยืนยันว่าตัวเลขเชื่อได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1584,11 +2032,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="8667750"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="12249150"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="รูป 37"/>
+        <xdr:cNvPr id="38" name="รูป 38"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1619,11 +2067,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="8972550"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="12496800"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="รูป 38"/>
+        <xdr:cNvPr id="39" name="รูป 39"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1649,7 +2097,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="0A3358"/>
               </a:solidFill>
@@ -1657,6 +2105,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>6. สำรอง แล้วทดลองกู้คืน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ดาวน์โหลดไฟล์ แล้วกู้คืนกลับจริง ๆ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ห้ามข้าม ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1664,11 +2138,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="5629275" y="9525000"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="6715125" y="13411200"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="รูป 39"/>
+        <xdr:cNvPr id="40" name="รูป 40"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1699,11 +2173,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4095750" y="9829800"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="4762500" y="13658850"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="รูป 40"/>
+        <xdr:cNvPr id="41" name="รูป 41"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1729,14 +2203,40 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="0A3358"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>7. ล้างข้อมูลทดลอง ใส่ยอดจริง</a:t>
+            <a:t>7. ล้างข้อมูลทดลอง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบเอกสารทดลองทั้งหมด แล้วใส่ยอดยกมาจริง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่ล้าง รายงานเดือนแรกจะมีตัวเลขทดลองปน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1744,11 +2244,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="571500"/>
-    <xdr:ext cx="3238500" cy="247650"/>
+    <xdr:pos x="9239250" y="1066800"/>
+    <xdr:ext cx="4095750" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="รูป 41"/>
+        <xdr:cNvPr id="42" name="รูป 42"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1770,7 +2270,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1100" b="1">
+            <a:rPr lang="th-TH" sz="1200" b="1">
               <a:solidFill>
                 <a:srgbClr val="2E7D52"/>
               </a:solidFill>
@@ -1778,6 +2278,19 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>D. ตั้งค่าในโปรแกรม</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ติดตั้งเสร็จแล้วยังใช้ทำงานจริงไม่ได้ ต้องตั้งค่าชุดนี้ก่อน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1785,11 +2298,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="876300"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="1504950"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="รูป 42"/>
+        <xdr:cNvPr id="43" name="รูป 43"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1815,7 +2328,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -1823,6 +2336,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>1. ข้อมูลกิจการ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ชื่อ ที่อยู่ เลขประจำตัวผู้เสียภาษี 13 หลัก สาขา</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ต้องมีก่อนออกเอกสารใบแรก</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1830,11 +2369,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="1428750"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="2419350"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="รูป 43"/>
+        <xdr:cNvPr id="44" name="รูป 44"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1865,11 +2404,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="1733550"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="2667000"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="รูป 44"/>
+        <xdr:cNvPr id="45" name="รูป 45"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1895,14 +2434,40 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>2. กลุ่มเอกสาร (รูปแบบเลขที่)</a:t>
+            <a:t>2. กลุ่มเอกสาร</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>รูปแบบเลขที่ เช่น IV-202609-0001</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เปลี่ยนทีหลัง เลขเก่าไม่เปลี่ยนตาม</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1910,11 +2475,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="2286000"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="3581400"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="รูป 45"/>
+        <xdr:cNvPr id="46" name="รูป 46"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1945,11 +2510,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="2590800"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="3829050"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="รูป 46"/>
+        <xdr:cNvPr id="47" name="รูป 47"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1975,7 +2540,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -1983,6 +2548,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>3. คลังและที่เก็บ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เพิ่มคลัง แล้วเพิ่มช่องเก็บในแต่ละคลัง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่มีคลัง รับสินค้าเข้าไม่ได้เลย</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1990,11 +2581,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="3143250"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="4743450"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="รูป 47"/>
+        <xdr:cNvPr id="48" name="รูป 48"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2025,11 +2616,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="3448050"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="4991100"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="รูป 48"/>
+        <xdr:cNvPr id="49" name="รูป 49"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2055,7 +2646,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -2063,6 +2654,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>4. กลุ่ม ยี่ห้อ ประเภทสินค้า</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ทะเบียนสามมิติสำหรับจำแนกสินค้า</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: รายการให้เลือกตอนเพิ่มสินค้า</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2070,11 +2687,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="4000500"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="5905500"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="รูป 49"/>
+        <xdr:cNvPr id="50" name="รูป 50"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2105,11 +2722,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="4305300"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="6153150"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="รูป 50"/>
+        <xdr:cNvPr id="51" name="รูป 51"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2135,7 +2752,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -2143,6 +2760,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>5. ข้อมูลสินค้า</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>รหัส ชื่อ หน่วยนับ ราคา บาร์โค๊ด (นำเข้าจาก Excel ได้ถ้ามีเยอะ)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: แกนของทั้งระบบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2150,11 +2793,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="4857750"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="7067550"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="รูป 51"/>
+        <xdr:cNvPr id="52" name="รูป 52"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2185,11 +2828,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="5162550"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="7315200"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="รูป 52"/>
+        <xdr:cNvPr id="53" name="รูป 53"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2215,7 +2858,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -2223,6 +2866,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>6. ยอดยกมา</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>รับสินค้าเข้าครั้งแรก หรือใช้ใบตรวจนับ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่ใส่ ระบบคิดว่าไม่มีของ แล้วขายไม่ได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2230,11 +2899,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="5715000"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="8229600"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="รูป 53"/>
+        <xdr:cNvPr id="54" name="รูป 54"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2265,11 +2934,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="6019800"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="8477250"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="รูป 54"/>
+        <xdr:cNvPr id="55" name="รูป 55"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2295,7 +2964,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -2303,6 +2972,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>7. ทะเบียนลูกค้าและเจ้าหนี้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>รหัส ชื่อ ที่อยู่แยกช่อง เลขผู้เสียภาษี</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ที่อยู่ต้องแยกช่อง เพราะรายงานกรองรายจังหวัด</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2310,11 +3005,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="6572250"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="9391650"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="รูป 55"/>
+        <xdr:cNvPr id="56" name="รูป 56"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2345,11 +3040,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="6877050"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="9639300"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="รูป 56"/>
+        <xdr:cNvPr id="57" name="รูป 57"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2375,7 +3070,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -2383,6 +3078,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>8. พนักงานขาย</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>รหัสและชื่อพนักงานขายทุกคน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ดูยอดขายรายคนและตั้งเป้ารายคนได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2390,11 +3111,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="7429500"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="10553700"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="รูป 57"/>
+        <xdr:cNvPr id="58" name="รูป 58"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2425,11 +3146,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="7734300"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="10801350"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="รูป 58"/>
+        <xdr:cNvPr id="59" name="รูป 59"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2455,7 +3176,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -2463,6 +3184,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>9. ผู้ใช้งานที่เหลือ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หนึ่งคนหนึ่งบัญชี ห้ามใช้ร่วมกัน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2470,11 +3217,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9439275" y="8286750"/>
-    <xdr:ext cx="171450" cy="247650"/>
+    <xdr:pos x="11191875" y="11715750"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="รูป 59"/>
+        <xdr:cNvPr id="60" name="รูป 60"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2505,11 +3252,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="7905750" y="8591550"/>
-    <xdr:ext cx="3238500" cy="495300"/>
+    <xdr:pos x="9239250" y="11963400"/>
+    <xdr:ext cx="4095750" cy="876300"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="60" name="รูป 60"/>
+        <xdr:cNvPr id="61" name="รูป 61"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2535,7 +3282,7 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1000" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
@@ -2543,6 +3290,32 @@
               <a:cs typeface="Tahoma"/>
             </a:rPr>
             <a:t>10. สิทธิการใช้งานรายคน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เลือกผู้ใช้ทีละคน ติ๊กว่าเห็นหน้าจอไหนและแก้ไขได้ไหม</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>คุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล (ดูชีต 8)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2550,11 +3323,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="10553700"/>
-    <xdr:ext cx="10858500" cy="495300"/>
+    <xdr:pos x="285750" y="14916150"/>
+    <xdr:ext cx="2857500" cy="228600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="รูป 61"/>
+        <xdr:cNvPr id="62" name="รูป 62"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2576,14 +3349,194 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1000">
+            <a:rPr lang="th-TH" sz="1100" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>คำอธิบายสี</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="15201900"/>
+    <xdr:ext cx="3143250" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="รูป 63"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>A. โครงของระบบ — รู้ไว้ ไม่ต้องทำอะไร</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="3619500" y="15201900"/>
+    <xdr:ext cx="3143250" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="รูป 64"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>B, D. ขั้นที่ต้องลงมือทำ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6953250" y="15201900"/>
+    <xdr:ext cx="3143250" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="รูป 65"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
               <a:solidFill>
                 <a:srgbClr val="5A3600"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>จำสองข้อนี้: Supabase ต้องมาก่อน Vercel เพราะขั้น Vercel ต้องใช้ค่าที่ได้จาก Supabase  ·  ใส่ค่าที่ Vercel แล้วต้อง Redeploy หนึ่งครั้ง ค่าใหม่ถึงจะมีผล</a:t>
+            <a:t>C. ค่าที่ต้องคัดลอกไปใส่</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10287000" y="15201900"/>
+    <xdr:ext cx="3143250" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="รูป 66"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>E. ขั้นตรวจรับ ทำหลังติดตั้งเสร็จ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2778,7 +3731,7 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFAU 3.3 · รอบ 97 (2026-09-12)</t>
+          <t xml:space="preserve">OFAU 3.3 · รอบ 98 (2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -4111,7 +5064,7 @@
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 97 (2026-09-12))</t>
+          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 98 (2026-09-12))</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="2">

--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -55,8 +55,8 @@
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="114300"/>
-    <xdr:ext cx="13049250" cy="438150"/>
+    <xdr:pos x="285750" y="95250"/>
+    <xdr:ext cx="13335000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="รูป 2"/>
@@ -101,7 +101,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>อ่านจากบนลงล่างทีละคอลัมน์ · บรรทัดล่างสุดของแต่ละกล่องคือผลที่ได้ ถ้าเป็นตัวหนาสีแดงคือข้อที่พลาดบ่อย</a:t>
+            <a:t>ถ้ายังไม่เคยติดตั้งมาก่อน ให้อ่านแผง “วิธีอ่านผังนี้” ข้างล่างก่อนหนึ่งรอบ แล้วค่อยเริ่มที่ผัง B</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -109,11 +109,263 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="590550"/>
-    <xdr:ext cx="13049250" cy="323850"/>
+    <xdr:pos x="285750" y="552450"/>
+    <xdr:ext cx="6572250" cy="2000250"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="รูป 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>วิธีอ่านผังนี้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หนึ่งกล่อง = หนึ่งขั้นที่ทำจบได้ในครั้งเดียว · อ่านจากบนลงล่างตามลูกศร</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950" b="1">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ในกล่องหนึ่งใบมี 4 บรรทัด เรียงจากบนลงล่าง:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>บรรทัด 1 (ตัวหนา)  ชื่อขั้น</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>บรรทัด 2           ทำอะไร ที่ไหน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>บรรทัด 3 (สีม่วง)   คำสั่งที่ต้องพิมพ์ ขั้นที่ทำบนเว็บจะไม่มีบรรทัดนี้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>บรรทัด 4           ขึ้นต้นว่า “ได้:” คือผลที่ได้ · ตัวหนาสีแดงคือข้อที่พลาดบ่อย</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7048500" y="552450"/>
+    <xdr:ext cx="6572250" cy="2000250"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="รูป 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>อ่านผังไหนก่อน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>A. ระบบประกอบด้วยอะไร   อ่านก่อนหนึ่งรอบ ให้รู้ว่าอะไรอยู่ที่ไหน (ไม่ต้องลงมือ)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>B. ลำดับการติดตั้ง       ลงมือทำตามตั้งแต่ขั้น 1 ถึง 5 ตามลำดับ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="8A5200"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>C. ค่าสองตัวไปไหนบ้าง     เปิดดูคู่กับผัง B ขั้นที่ 2 และ 4 เป็นผังอ้างอิง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>D. ตั้งค่าในโปรแกรม      ทำหลังล็อกอินเข้าระบบได้แล้ว</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>E. ตรวจรับก่อนเปิดใช้จริง  ทำเป็นอย่างสุดท้าย ก่อนให้พนักงานเริ่มใช้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ติดตรงไหนก็สั่ง  npm run setup  ได้ตลอด มันบอกเองว่าเหลืออะไร</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="2667000"/>
+    <xdr:ext cx="13335000" cy="342900"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="รูป 5"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -146,7 +398,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>จำสองข้อนี้ก่อน:  Supabase ต้องมาก่อน Vercel เพราะขั้น Vercel ต้องใช้ค่าที่ได้จาก Supabase   ·   ใส่ค่าที่ Vercel แล้วต้อง Redeploy หนึ่งครั้ง ค่าใหม่ถึงจะมีผล</a:t>
+            <a:t>สองข้อที่คนพลาดบ่อยที่สุด:  Supabase ต้องมาก่อน Vercel เพราะขั้น Vercel ต้องใช้ค่าที่ได้จาก Supabase   ·   ใส่ค่าที่ Vercel แล้วต้องกด Redeploy หนึ่งครั้ง ค่าใหม่ถึงจะมีผล</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -154,11 +406,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="1066800"/>
-    <xdr:ext cx="4095750" cy="381000"/>
+    <xdr:pos x="285750" y="3200400"/>
+    <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="รูป 4"/>
+        <xdr:cNvPr id="6" name="รูป 6"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -180,7 +432,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1200" b="1">
+            <a:rPr lang="th-TH" sz="1250" b="1">
               <a:solidFill>
                 <a:srgbClr val="8A978F"/>
               </a:solidFill>
@@ -200,7 +452,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สามส่วนนี้อยู่คนละที่ ไม่ได้อยู่เครื่องเดียวกัน</a:t>
+            <a:t>อ่านให้เข้าใจก่อน ยังไม่ต้องลงมือทำ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -208,114 +460,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="1504950"/>
-    <xdr:ext cx="4095750" cy="876300"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="รูป 5"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EFF1F0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ผู้ใช้</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เปิดเว็บผ่านเบราว์เซอร์ ที่อยู่ของ Vercel</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B756F"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: หน้าเว็บของระบบ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2238375" y="2419350"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="รูป 6"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="8A978F"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="2667000"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="285750" y="3638550"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="7" name="รูป 7"/>
@@ -351,7 +497,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Vercel — ที่รันเว็บ</a:t>
+            <a:t>ผู้ใช้ (เบราว์เซอร์)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -364,7 +510,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เอาโค้ดจาก GitHub มารันเอง ทุกครั้งที่ push</a:t>
+            <a:t>เปิดเว็บตามที่อยู่ของ Vercel</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -377,7 +523,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เก็บเฉพาะโค้ด ไม่มีข้อมูลของกิจการอยู่เลย</a:t>
+            <a:t>ได้: หน้าเว็บของระบบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -385,7 +531,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="2238375" y="3581400"/>
+    <xdr:pos x="2286000" y="4667250"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -420,8 +566,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="3829050"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="285750" y="4914900"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="9" name="รูป 9"/>
@@ -457,7 +603,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Supabase — ฐานข้อมูล + ล็อกอิน</a:t>
+            <a:t>Vercel — ที่รันเว็บ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -470,20 +616,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เก็บข้อมูลจริงทั้งหมด และตรวจรหัสผ่านตอนล็อกอิน</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ลบโปรเจกต์นี้เมื่อไร ข้อมูลหายทั้งหมดทันที</a:t>
+            <a:t>เอาโค้ดจาก GitHub มารันเอง ทุกครั้งที่ push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บเฉพาะโค้ด ไม่มีข้อมูลของกิจการอยู่เลย</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -491,11 +637,117 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="5086350"/>
-    <xdr:ext cx="4095750" cy="381000"/>
+    <xdr:pos x="2286000" y="5943600"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="10" name="รูป 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8A978F"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="6191250"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="รูป 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Supabase — ฐานข้อมูล + ล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บข้อมูลจริงทั้งหมด และตรวจรหัสผ่านตอนล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบโปรเจกต์นี้เมื่อไร ข้อมูลหายทั้งหมดทันที</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="7600950"/>
+    <xdr:ext cx="4191000" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="รูป 12"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -517,7 +769,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1200" b="1">
+            <a:rPr lang="th-TH" sz="1250" b="1">
               <a:solidFill>
                 <a:srgbClr val="2E7D52"/>
               </a:solidFill>
@@ -537,7 +789,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ห้าขั้น ข้ามลำดับไม่ได้</a:t>
+            <a:t>ลงมือทำตามนี้ ขั้น 1 ถึง 5 ห้ามข้ามลำดับ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -545,114 +797,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="5524500"/>
-    <xdr:ext cx="4095750" cy="876300"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="รูป 11"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. เตรียมโค้ด</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>git clone มาเป็นโปรเจกต์ใหม่</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: โฟลเดอร์ที่มีไฟล์ครบ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2238375" y="6438900"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="รูป 12"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="6686550"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="285750" y="8039100"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="13" name="รูป 13"/>
@@ -688,7 +834,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>2. Supabase</a:t>
+            <a:t>1. เตรียมโค้ด</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -701,20 +847,33 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้างโปรเจกต์ (Region สิงคโปร์) · รัน schema.sql ทั้งไฟล์ · สร้างผู้ใช้คนแรก</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ตอนสร้างผู้ใช้ ต้องติ๊ก Auto Confirm User</a:t>
+            <a:t>คัดลอกโค้ดมาเป็นโปรเจกต์ใหม่ แล้วเข้าไปในโฟลเดอร์</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git clone &lt;repo&gt; ชื่อใหม่</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: โฟลเดอร์ที่มีไฟล์ครบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -722,7 +881,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="2238375" y="7600950"/>
+    <xdr:pos x="2286000" y="9067800"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -757,8 +916,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="7848600"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="285750" y="9315450"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="15" name="รูป 15"/>
@@ -794,7 +953,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. GitHub</a:t>
+            <a:t>2. Supabase (ทำบนเว็บ)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -807,20 +966,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้าง repo (ตั้ง Private) แล้ว push โค้ดขึ้นไป</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ที่อยู่ repo ให้ Vercel ไปอ่าน</a:t>
+            <a:t>สร้างโปรเจกต์ Region สิงคโปร์ · SQL Editor วาง schema.sql ทั้งไฟล์ กด Run · Add user</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ตอนสร้างผู้ใช้ ต้องติ๊ก Auto Confirm User</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -828,7 +987,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="2238375" y="8763000"/>
+    <xdr:pos x="2286000" y="10344150"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -863,8 +1022,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="9010650"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="285750" y="10591800"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="17" name="รูป 17"/>
@@ -900,7 +1059,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. Vercel</a:t>
+            <a:t>3. ตรวจก่อนไปต่อ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -913,20 +1072,33 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้างโปรเจกต์จาก repo · ใส่ค่าสองตัวจากขั้น 2 · ติ๊กครบ 3 environment</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ใส่ค่าแล้วต้อง Redeploy หนึ่งครั้ง</a:t>
+            <a:t>สร้างไฟล์ค่าในเครื่อง ใส่ค่าสองตัวจากขั้น 2 แล้วสั่งตรวจ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run setup -- --init</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: รู้ทันทีว่าฐานข้อมูลพร้อมหรือยัง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -934,7 +1106,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="2238375" y="9925050"/>
+    <xdr:pos x="2286000" y="11620500"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -969,8 +1141,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="10172700"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="285750" y="11868150"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="19" name="รูป 19"/>
@@ -1006,7 +1178,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. เปิดเว็บ ล็อกอิน</a:t>
+            <a:t>4. ขึ้น GitHub</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1019,20 +1191,33 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ใช้อีเมลและรหัสผ่านที่สร้างไว้ในขั้น 2</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ล็อกอินไม่ได้ ให้สั่ง npm run setup ก่อน</a:t>
+            <a:t>สร้าง repo ตั้งเป็น Private แล้ว push โค้ดขึ้นไป</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git add -A &amp;&amp; git commit -m "เริ่ม" &amp;&amp; git push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ที่อยู่ repo ให้ Vercel ไปอ่าน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1040,11 +1225,117 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="1066800"/>
-    <xdr:ext cx="4095750" cy="381000"/>
+    <xdr:pos x="2286000" y="12896850"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="20" name="รูป 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="13144500"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="รูป 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>5. Vercel (ทำบนเว็บ)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Add New Project เลือก repo · ใส่ค่าสองตัว ติ๊กครบ 3 environment · Deploy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ค่าแล้วต้องกด Redeploy หนึ่งครั้ง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="3200400"/>
+    <xdr:ext cx="4191000" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="รูป 22"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1066,7 +1357,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1200" b="1">
+            <a:rPr lang="th-TH" sz="1250" b="1">
               <a:solidFill>
                 <a:srgbClr val="B26A00"/>
               </a:solidFill>
@@ -1086,7 +1377,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ค่าเดียวกัน ต้องใส่สองที่</a:t>
+            <a:t>เปิดดูคู่กับผัง B ขั้นที่ 2 และ 5</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1094,114 +1385,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="1504950"/>
-    <xdr:ext cx="4095750" cy="876300"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="รูป 21"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FBF0E0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ต้นทาง: Supabase</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>Project Settings &gt; API · คัดลอก Project URL และ anon public key</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ห้ามหยิบ service_role มาใส่แทน anon key</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="2419350"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="รูป 22"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="B26A00"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="2667000"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="3638550"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="23" name="รูป 23"/>
@@ -1237,7 +1422,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ปลายทาง 1: .env.local</a:t>
+            <a:t>ต้นทาง: Supabase</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1250,7 +1435,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ไฟล์ในเครื่องตัวเอง ใช้ตอนสั่ง npm run dev</a:t>
+            <a:t>Project Settings &gt; API · คัดลอก Project URL และ anon public key</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1263,7 +1448,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ไฟล์นี้ต้องไม่ขึ้น git เด็ดขาด</a:t>
+            <a:t>ห้ามหยิบ service_role มาใส่แทน anon key</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1271,7 +1456,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="3581400"/>
+    <xdr:pos x="6858000" y="4667250"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1306,8 +1491,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="3829050"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="4914900"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="25" name="รูป 25"/>
@@ -1343,7 +1528,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ปลายทาง 2: Vercel</a:t>
+            <a:t>ปลายทาง 1: ไฟล์ .env.local</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1356,7 +1541,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Environment Variables · ติ๊กครบ Production, Preview, Development</a:t>
+            <a:t>ไฟล์ในเครื่องตัวเอง ใช้ตอนรันในเครื่อง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run setup -- --init</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1369,7 +1567,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ใส่ที่เครื่องอย่างเดียว เว็บจริงยังล็อกอินไม่ได้</a:t>
+            <a:t>ไฟล์นี้ต้องไม่ขึ้น git เด็ดขาด</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1377,7 +1575,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="4743450"/>
+    <xdr:pos x="6858000" y="5943600"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1412,8 +1610,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="4991100"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="6191250"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="27" name="รูป 27"/>
@@ -1449,7 +1647,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Redeploy หนึ่งครั้ง</a:t>
+            <a:t>ปลายทาง 2: Vercel</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1462,20 +1660,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Vercel &gt; Deployments &gt; Redeploy</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="8A5200"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ค่าถูกฝังลงไฟล์ที่เบราว์เซอร์โหลด</a:t>
+            <a:t>Environment Variables · ติ๊กครบ Production, Preview, Development</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ที่เครื่องอย่างเดียว เว็บจริงยังล็อกอินไม่ได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1483,11 +1681,117 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="6248400"/>
-    <xdr:ext cx="4095750" cy="381000"/>
+    <xdr:pos x="6858000" y="7219950"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="28" name="รูป 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="B26A00"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="7467600"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="รูป 29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>กด Redeploy หนึ่งครั้ง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel &gt; Deployments &gt; Redeploy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="8A5200"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ค่าถูกฝังลงไฟล์ที่เบราว์เซอร์โหลด</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="8877300"/>
+    <xdr:ext cx="4191000" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="รูป 30"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1509,7 +1813,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1200" b="1">
+            <a:rPr lang="th-TH" sz="1250" b="1">
               <a:solidFill>
                 <a:srgbClr val="0B5FA5"/>
               </a:solidFill>
@@ -1529,7 +1833,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เดินงานจริงหนึ่งรอบก่อนเสมอ</a:t>
+            <a:t>เดินงานจริงหนึ่งรอบ ก่อนให้พนักงานเริ่มใช้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1537,114 +1841,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="6686550"/>
-    <xdr:ext cx="4095750" cy="876300"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="รูป 29"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="E7F0FA"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. ซื้อ 1 ใบ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>บันทึกใบซื้อทดลองที่หน้าซื้อสินค้าและบริการ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="0B5FA5"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ของเข้าคลัง ยอดคงเหลือเพิ่ม</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="7600950"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="รูป 30"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="0B5FA5"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="7848600"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="9315450"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="31" name="รูป 31"/>
@@ -1680,7 +1878,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>2. ตรวจยอดคงเหลือ</a:t>
+            <a:t>1. ซื้อ 1 ใบ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1693,7 +1891,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เปิดหน้าข้อมูลสินค้า ดูรายคลังรายช่องเก็บ</a:t>
+            <a:t>หน้าซื้อสินค้าและบริการ บันทึกใบซื้อทดลอง</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1706,7 +1904,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ยืนยันว่าของเข้าถูกที่</a:t>
+            <a:t>ได้: ของเข้าคลัง ยอดคงเหลือเพิ่ม</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1714,7 +1912,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="8763000"/>
+    <xdr:pos x="6858000" y="10344150"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1749,8 +1947,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="9010650"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="10591800"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="33" name="รูป 33"/>
@@ -1786,7 +1984,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. ขาย POS 1 บิล</a:t>
+            <a:t>2. ตรวจยอดคงเหลือ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1799,7 +1997,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ยิงบาร์โค๊ด คิดเงิน พิมพ์ใบเสร็จ</a:t>
+            <a:t>หน้าข้อมูลสินค้า ดูรายคลังรายช่องเก็บ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1812,7 +2010,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ยอดคงเหลือลดลงตามจริง</a:t>
+            <a:t>ได้: ยืนยันว่าของเข้าถูกที่</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1820,7 +2018,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="9925050"/>
+    <xdr:pos x="6858000" y="11620500"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1855,8 +2053,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="10172700"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="11868150"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="35" name="รูป 35"/>
@@ -1892,7 +2090,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. ออกใบกำกับภาษี 1 ใบ</a:t>
+            <a:t>3. ขาย POS 1 บิล</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1905,20 +2103,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ตรวจหัวเอกสารว่าชื่อกิจการและเลขผู้เสียภาษีถูก</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หัวเอกสารผิด = ยังไม่ได้ตั้งข้อมูลกิจการ</a:t>
+            <a:t>ยิงบาร์โค๊ด คิดเงิน พิมพ์ใบเสร็จ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยอดคงเหลือลดลงตามจริง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1926,7 +2124,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="11087100"/>
+    <xdr:pos x="6858000" y="12896850"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1961,8 +2159,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="11334750"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="13144500"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="37" name="รูป 37"/>
@@ -1998,7 +2196,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. ดูรายงานว่ายอดตรง</a:t>
+            <a:t>4. ออกใบกำกับภาษี 1 ใบ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2011,20 +2209,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เทียบกับที่ทดลองทำไปทุกใบ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="0B5FA5"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ยืนยันว่าตัวเลขเชื่อได้</a:t>
+            <a:t>ตรวจหัวเอกสารว่าชื่อกิจการและเลขผู้เสียภาษีถูก</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หัวเอกสารผิด = ยังไม่ได้ตั้งข้อมูลกิจการ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2032,7 +2230,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="12249150"/>
+    <xdr:pos x="6858000" y="14173200"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2067,8 +2265,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="12496800"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="14420850"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="39" name="รูป 39"/>
@@ -2104,7 +2302,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>6. สำรอง แล้วทดลองกู้คืน</a:t>
+            <a:t>5. ดูรายงานว่ายอดตรง</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2117,20 +2315,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ดาวน์โหลดไฟล์ แล้วกู้คืนกลับจริง ๆ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ห้ามข้าม ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง</a:t>
+            <a:t>เทียบกับที่ทดลองทำไปทุกใบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยืนยันว่าตัวเลขเชื่อได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2138,7 +2336,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6715125" y="13411200"/>
+    <xdr:pos x="6858000" y="15449550"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2173,8 +2371,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="13658850"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="4857750" y="15697200"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="41" name="รูป 41"/>
@@ -2210,7 +2408,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>7. ล้างข้อมูลทดลอง</a:t>
+            <a:t>6. สำรอง แล้วทดลองกู้คืน</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2223,7 +2421,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ลบเอกสารทดลองทั้งหมด แล้วใส่ยอดยกมาจริง</a:t>
+            <a:t>หน้าสำรองข้อมูล ดาวน์โหลดไฟล์ แล้วกู้คืนกลับจริง ๆ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2236,7 +2434,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ไม่ล้าง รายงานเดือนแรกจะมีตัวเลขทดลองปน</a:t>
+            <a:t>ห้ามข้าม ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2244,11 +2442,117 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="1066800"/>
-    <xdr:ext cx="4095750" cy="381000"/>
+    <xdr:pos x="6858000" y="16725900"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="42" name="รูป 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="16973550"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="รูป 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>7. ล้างข้อมูลทดลอง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบเอกสารทดลองทั้งหมด แล้วใส่ยอดยกมาจริง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่ล้าง รายงานเดือนแรกจะมีตัวเลขทดลองปน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="3200400"/>
+    <xdr:ext cx="4191000" cy="381000"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="รูป 44"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2270,7 +2574,7 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1200" b="1">
+            <a:rPr lang="th-TH" sz="1250" b="1">
               <a:solidFill>
                 <a:srgbClr val="2E7D52"/>
               </a:solidFill>
@@ -2290,7 +2594,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ติดตั้งเสร็จแล้วยังใช้ทำงานจริงไม่ได้ ต้องตั้งค่าชุดนี้ก่อน</a:t>
+            <a:t>ทำหลังล็อกอินได้แล้ว ทุกขั้นทำในโปรแกรม ไม่มีคำสั่ง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2298,114 +2602,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="1504950"/>
-    <xdr:ext cx="4095750" cy="876300"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="รูป 43"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. ข้อมูลกิจการ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ชื่อ ที่อยู่ เลขประจำตัวผู้เสียภาษี 13 หลัก สาขา</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ต้องมีก่อนออกเอกสารใบแรก</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="2419350"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="รูป 44"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="2667000"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="3638550"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="45" name="รูป 45"/>
@@ -2441,7 +2639,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>2. กลุ่มเอกสาร</a:t>
+            <a:t>1. ข้อมูลกิจการ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2454,7 +2652,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รูปแบบเลขที่ เช่น IV-202609-0001</a:t>
+            <a:t>ชื่อ ที่อยู่ เลขประจำตัวผู้เสียภาษี 13 หลัก สาขา</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2467,7 +2665,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เปลี่ยนทีหลัง เลขเก่าไม่เปลี่ยนตาม</a:t>
+            <a:t>ต้องมีก่อนออกเอกสารใบแรก</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2475,7 +2673,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="3581400"/>
+    <xdr:pos x="11430000" y="4667250"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2510,8 +2708,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="3829050"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="4914900"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="47" name="รูป 47"/>
@@ -2547,7 +2745,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. คลังและที่เก็บ</a:t>
+            <a:t>2. กลุ่มเอกสาร</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2560,7 +2758,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เพิ่มคลัง แล้วเพิ่มช่องเก็บในแต่ละคลัง</a:t>
+            <a:t>รูปแบบเลขที่ เช่น IV-202609-0001</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2573,7 +2771,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ไม่มีคลัง รับสินค้าเข้าไม่ได้เลย</a:t>
+            <a:t>เปลี่ยนทีหลัง เลขเก่าไม่เปลี่ยนตาม</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2581,7 +2779,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="4743450"/>
+    <xdr:pos x="11430000" y="5943600"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2616,8 +2814,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="4991100"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="6191250"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="49" name="รูป 49"/>
@@ -2653,7 +2851,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. กลุ่ม ยี่ห้อ ประเภทสินค้า</a:t>
+            <a:t>3. คลังและที่เก็บ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2666,20 +2864,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ทะเบียนสามมิติสำหรับจำแนกสินค้า</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: รายการให้เลือกตอนเพิ่มสินค้า</a:t>
+            <a:t>เพิ่มคลัง แล้วเพิ่มช่องเก็บในแต่ละคลัง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่มีคลัง รับสินค้าเข้าไม่ได้เลย</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2687,7 +2885,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="5905500"/>
+    <xdr:pos x="11430000" y="7219950"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2722,8 +2920,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="6153150"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="7467600"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="51" name="รูป 51"/>
@@ -2759,7 +2957,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. ข้อมูลสินค้า</a:t>
+            <a:t>4. กลุ่ม ยี่ห้อ ประเภทสินค้า</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2772,7 +2970,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัส ชื่อ หน่วยนับ ราคา บาร์โค๊ด (นำเข้าจาก Excel ได้ถ้ามีเยอะ)</a:t>
+            <a:t>ทะเบียนสามมิติสำหรับจำแนกสินค้า</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2785,7 +2983,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: แกนของทั้งระบบ</a:t>
+            <a:t>ได้: รายการให้เลือกตอนเพิ่มสินค้า</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2793,7 +2991,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="7067550"/>
+    <xdr:pos x="11430000" y="8496300"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2828,8 +3026,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="7315200"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="8743950"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="53" name="รูป 53"/>
@@ -2865,7 +3063,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>6. ยอดยกมา</a:t>
+            <a:t>5. ข้อมูลสินค้า</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2878,20 +3076,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รับสินค้าเข้าครั้งแรก หรือใช้ใบตรวจนับ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไม่ใส่ ระบบคิดว่าไม่มีของ แล้วขายไม่ได้</a:t>
+            <a:t>รหัส ชื่อ หน่วยนับ ราคา บาร์โค๊ด · นำเข้าจาก Excel ได้ถ้ามีเยอะ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: แกนของทั้งระบบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2899,7 +3097,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="8229600"/>
+    <xdr:pos x="11430000" y="9772650"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2934,8 +3132,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="8477250"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="10020300"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="55" name="รูป 55"/>
@@ -2971,7 +3169,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>7. ทะเบียนลูกค้าและเจ้าหนี้</a:t>
+            <a:t>6. ยอดยกมา</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2984,20 +3182,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัส ชื่อ ที่อยู่แยกช่อง เลขผู้เสียภาษี</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ที่อยู่ต้องแยกช่อง เพราะรายงานกรองรายจังหวัด</a:t>
+            <a:t>รับสินค้าเข้าครั้งแรก หรือใช้ใบตรวจนับ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่ใส่ ระบบคิดว่าไม่มีของ แล้วขายไม่ได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3005,7 +3203,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="9391650"/>
+    <xdr:pos x="11430000" y="11049000"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3040,8 +3238,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="9639300"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="11296650"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="57" name="รูป 57"/>
@@ -3077,7 +3275,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>8. พนักงานขาย</a:t>
+            <a:t>7. ทะเบียนลูกค้าและเจ้าหนี้</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3090,7 +3288,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัสและชื่อพนักงานขายทุกคน</a:t>
+            <a:t>รหัส ชื่อ ที่อยู่แยกช่อง เลขผู้เสียภาษี</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3103,7 +3301,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ดูยอดขายรายคนและตั้งเป้ารายคนได้</a:t>
+            <a:t>ได้: ข้อมูลผู้ซื้อผู้ขายบนเอกสาร</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3111,7 +3309,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="10553700"/>
+    <xdr:pos x="11430000" y="12325350"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3146,8 +3344,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="10801350"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="12573000"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="59" name="รูป 59"/>
@@ -3183,7 +3381,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>9. ผู้ใช้งานที่เหลือ</a:t>
+            <a:t>8. พนักงานขาย</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3196,20 +3394,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หนึ่งคนหนึ่งบัญชี ห้ามใช้ร่วมกัน</a:t>
+            <a:t>รหัสและชื่อพนักงานขายทุกคน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ดูยอดขายรายคนและตั้งเป้ารายคนได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3217,7 +3415,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11191875" y="11715750"/>
+    <xdr:pos x="11430000" y="13601700"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3252,8 +3450,8 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="11963400"/>
-    <xdr:ext cx="4095750" cy="876300"/>
+    <xdr:pos x="9429750" y="13849350"/>
+    <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="61" name="รูป 61"/>
@@ -3289,7 +3487,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>10. สิทธิการใช้งานรายคน</a:t>
+            <a:t>9. ผู้ใช้งานที่เหลือ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3302,7 +3500,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เลือกผู้ใช้ทีละคน ติ๊กว่าเห็นหน้าจอไหนและแก้ไขได้ไหม</a:t>
+            <a:t>สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3315,7 +3513,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>คุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล (ดูชีต 8)</a:t>
+            <a:t>หนึ่งคนหนึ่งบัญชี ห้ามใช้ร่วมกัน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3323,11 +3521,117 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="14916150"/>
-    <xdr:ext cx="2857500" cy="228600"/>
+    <xdr:pos x="11430000" y="14878050"/>
+    <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="62" name="รูป 62"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="15125700"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="63" name="รูป 63"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>10. สิทธิการใช้งานรายคน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เลือกผู้ใช้ทีละคน ติ๊กว่าเห็นหน้าจอไหนและแก้ไขได้ไหม</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>คุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล (ดูชีต 8)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="18383250"/>
+    <xdr:ext cx="4762500" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="รูป 64"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3349,14 +3653,14 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="th-TH" sz="1100" b="1">
+            <a:rPr lang="th-TH" sz="1250" b="1">
               <a:solidFill>
                 <a:srgbClr val="1B3D2A"/>
               </a:solidFill>
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>คำอธิบายสี</a:t>
+            <a:t>คำสั่งที่ต้องใช้ (พิมพ์ในโฟลเดอร์โปรเจกต์)</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3364,11 +3668,499 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="15201900"/>
+    <xdr:pos x="285750" y="18688050"/>
+    <xdr:ext cx="4191000" cy="1676400"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="รูป 65"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F6F3FB"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="5B21B6"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1050" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ตอนติดตั้ง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git clone &lt;repo&gt; ชื่อใหม่</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      คัดลอกโค้ดมาเป็นโปรเจกต์ใหม่</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm install</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      ลงไลบรารี ทำครั้งเดียวตอนเริ่ม</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run setup -- --init</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      สร้างไฟล์ .env.local ให้ แล้วบอกว่าต้องใส่ค่าอะไร</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run setup</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      ตรวจว่าติดตั้งถึงไหนแล้ว และเหลืออะไรต้องทำ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4762500" y="18688050"/>
+    <xdr:ext cx="4191000" cy="1676400"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="รูป 66"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F6F3FB"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="5B21B6"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1050" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ตอนทำงานประจำ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run dev</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      รันเว็บในเครื่องที่ localhost:3000</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run check</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      ตรวจความเรียบร้อยทั้งโปรเจกต์ ทำก่อน commit ทุกครั้ง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git add -A</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      เอาไฟล์ที่แก้ทั้งหมดเข้าคิว</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git commit -m "ข้อความ"</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      บันทึกการแก้ไขหนึ่งชุด</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9239250" y="18688050"/>
+    <xdr:ext cx="4191000" cy="1676400"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="67" name="รูป 67"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F6F3FB"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="5B21B6"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1050" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ตอนส่งขึ้นเว็บจริง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      ส่งขึ้น GitHub · Vercel จะ deploy ให้เองทันที</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git pull</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      ดึงรุ่นใหม่ลงเครื่อง ทำก่อนเริ่มแก้ทุกครั้ง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git status</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      ดูว่าแก้ไฟล์อะไรไปบ้าง และ .env.local ไม่หลุดเข้ามา</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="950">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git log --oneline -10</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>      ดูประวัติสิบรายการล่าสุด</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="20745450"/>
+    <xdr:ext cx="2857500" cy="228600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="68" name="รูป 68"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1150" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>คำอธิบายสีของกล่อง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="21031200"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="รูป 63"/>
+        <xdr:cNvPr id="69" name="รูป 69"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3401,7 +4193,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>A. โครงของระบบ — รู้ไว้ ไม่ต้องทำอะไร</a:t>
+            <a:t>เทา = โครงของระบบ รู้ไว้ ไม่ต้องทำ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3409,11 +4201,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="3619500" y="15201900"/>
+    <xdr:pos x="3619500" y="21031200"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="64" name="รูป 64"/>
+        <xdr:cNvPr id="70" name="รูป 70"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3446,7 +4238,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>B, D. ขั้นที่ต้องลงมือทำ</a:t>
+            <a:t>เขียว = ขั้นที่ต้องลงมือทำ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3454,11 +4246,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6953250" y="15201900"/>
+    <xdr:pos x="6953250" y="21031200"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="65" name="รูป 65"/>
+        <xdr:cNvPr id="71" name="รูป 71"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3491,7 +4283,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>C. ค่าที่ต้องคัดลอกไปใส่</a:t>
+            <a:t>เหลือง = ค่าที่ต้องคัดลอกไปใส่</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3499,11 +4291,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="10287000" y="15201900"/>
+    <xdr:pos x="10287000" y="21031200"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="66" name="รูป 66"/>
+        <xdr:cNvPr id="72" name="รูป 72"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3536,7 +4328,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>E. ขั้นตรวจรับ ทำหลังติดตั้งเสร็จ</a:t>
+            <a:t>ฟ้า = ขั้นตรวจรับ ทำเป็นอย่างสุดท้าย</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3731,7 +4523,7 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFAU 3.3 · รอบ 98 (2026-09-12)</t>
+          <t xml:space="preserve">OFAU 3.3 · รอบ 99 (2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5856,7 @@
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 98 (2026-09-12))</t>
+          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 99 (2026-09-12))</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="2">

--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -361,11 +361,604 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="2667000"/>
+    <xdr:pos x="285750" y="2686050"/>
+    <xdr:ext cx="13335000" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="รูป 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1250" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>สามบริการนี้ไว้ทำอะไร — โค้ดอยู่ที่ GitHub · รันที่ Vercel · ข้อมูลอยู่ที่ Supabase</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="2990850"/>
+    <xdr:ext cx="4191000" cy="2400300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="รูป 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="8A978F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>GitHub</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ที่เก็บโค้ดและประวัติการแก้ไข</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="8A978F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บอะไรไว้ที่นี่</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไฟล์โค้ดทั้งหมด และประวัติทุกครั้งที่ commit</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="8A978F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ทำอะไรให้เรา</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  ย้อนกลับไปรุ่นก่อนหน้าได้ เมื่อแก้แล้วพัง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  เป็นตัวสั่งให้ Vercel deploy ทุกครั้งที่ push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  ทำงานหลายคนพร้อมกันได้ โดยไม่ทับงานกัน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่มีข้อมูลของกิจการอยู่เลย ไม่มีสินค้า ลูกค้า หรือเอกสารสักใบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบทิ้ง: โค้ดยังอยู่ในเครื่อง แต่ Vercel จะ deploy ต่อไม่ได้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ฟรี · ตั้งเป็น Private ได้</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="2990850"/>
+    <xdr:ext cx="4191000" cy="2400300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="รูป 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ที่รันเว็บ ให้คนเปิดใช้จากที่ไหนก็ได้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บอะไรไว้ที่นี่</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>โค้ดรุ่นล่าสุดที่ build แล้ว และค่า Environment Variables</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ทำอะไรให้เรา</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  deploy ให้เองทุกครั้งที่ push ขึ้น GitHub</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  ให้โดเมนและ HTTPS มาพร้อม ไม่ต้องตั้งเอง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  รันส่วนที่ต้องทำฝั่งเซิร์ฟเวอร์ เช่น ตัวรับข้อความจากไลน์</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่มีข้อมูลของกิจการอยู่เลย เป็นแค่ที่รันโค้ด</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบทิ้ง: เว็บเปิดไม่ได้ แต่ข้อมูลไม่หาย สร้างใหม่แล้วต่อกลับได้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ฟรีสำหรับการใช้งานทั่วไป</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="2990850"/>
+    <xdr:ext cx="4191000" cy="2400300"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="รูป 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Supabase</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ฐานข้อมูลและระบบล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บอะไรไว้ที่นี่</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ข้อมูลจริงทั้งหมด 44 ตาราง และบัญชีผู้ใช้กับรหัสผ่าน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ทำอะไรให้เรา</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  เก็บและค้นข้อมูลทุกอย่าง สินค้า คลัง ลูกค้า เอกสารทุกใบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  ตรวจอีเมลกับรหัสผ่านตอนล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>·  คุมสิทธิ์ด้วย RLS ว่าใครอ่านและเขียนอะไรได้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ทุกอย่างที่เป็นข้อมูลของกิจการอยู่ที่นี่ที่เดียว</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบทิ้ง: ข้อมูลหายทั้งหมดทันที ต้องกู้จากไฟล์สำรองที่ทำไว้เอง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ฟรี · ไม่มีคนใช้เกิน 7 วันจะถูก pause ให้เข้า Dashboard กด Restore</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="5543550"/>
     <xdr:ext cx="13335000" cy="342900"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="รูป 5"/>
+        <xdr:cNvPr id="9" name="รูป 9"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -406,11 +999,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="3200400"/>
+    <xdr:pos x="285750" y="6076950"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="รูป 6"/>
+        <xdr:cNvPr id="10" name="รูป 10"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -439,7 +1032,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>A. ระบบประกอบด้วยอะไร</a:t>
+            <a:t>A. ของไหลไปทางไหน</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -452,7 +1045,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>อ่านให้เข้าใจก่อน ยังไม่ต้องลงมือทำ</a:t>
+            <a:t>รายละเอียดของแต่ละบริการดูที่แผงด้านบน</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -460,219 +1053,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="3638550"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="รูป 7"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EFF1F0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ผู้ใช้ (เบราว์เซอร์)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เปิดเว็บตามที่อยู่ของ Vercel</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B756F"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: หน้าเว็บของระบบ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="4667250"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="รูป 8"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="8A978F"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="4914900"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="รูป 9"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EFF1F0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>Vercel — ที่รันเว็บ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เอาโค้ดจาก GitHub มารันเอง ทุกครั้งที่ push</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B756F"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เก็บเฉพาะโค้ด ไม่มีข้อมูลของกิจการอยู่เลย</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="5943600"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="รูป 10"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="8A978F"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="6191250"/>
+    <xdr:pos x="285750" y="6515100"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -709,7 +1090,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Supabase — ฐานข้อมูล + ล็อกอิน</a:t>
+            <a:t>ผู้ใช้ (เบราว์เซอร์)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -722,20 +1103,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เก็บข้อมูลจริงทั้งหมด และตรวจรหัสผ่านตอนล็อกอิน</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ลบโปรเจกต์นี้เมื่อไร ข้อมูลหายทั้งหมดทันที</a:t>
+            <a:t>เปิดเว็บตามที่อยู่ของ Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: หน้าเว็บของระบบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -743,11 +1124,223 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="7600950"/>
+    <xdr:pos x="2286000" y="7543800"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="รูป 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8A978F"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="7791450"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="รูป 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel — ที่รันเว็บ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เอาโค้ดจาก GitHub มารันเอง ทุกครั้งที่ push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บเฉพาะโค้ด ไม่มีข้อมูลของกิจการอยู่เลย</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2286000" y="8820150"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="รูป 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8A978F"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="9067800"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="รูป 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Supabase — ฐานข้อมูล + ล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บข้อมูลจริงทั้งหมด และตรวจรหัสผ่านตอนล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบโปรเจกต์นี้เมื่อไร ข้อมูลหายทั้งหมดทันที</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="10477500"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="รูป 12"/>
+        <xdr:cNvPr id="16" name="รูป 16"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -797,232 +1390,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="8039100"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="รูป 13"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. เตรียมโค้ด</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>คัดลอกโค้ดมาเป็นโปรเจกต์ใหม่ แล้วเข้าไปในโฟลเดอร์</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5B21B6"/>
-              </a:solidFill>
-              <a:latin typeface="Consolas"/>
-              <a:cs typeface="Consolas"/>
-            </a:rPr>
-            <a:t>git clone &lt;repo&gt; ชื่อใหม่</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: โฟลเดอร์ที่มีไฟล์ครบ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="9067800"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="รูป 14"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="9315450"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="รูป 15"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>2. Supabase (ทำบนเว็บ)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>สร้างโปรเจกต์ Region สิงคโปร์ · SQL Editor วาง schema.sql ทั้งไฟล์ กด Run · Add user</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ตอนสร้างผู้ใช้ ต้องติ๊ก Auto Confirm User</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="10344150"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="รูป 16"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="10591800"/>
+    <xdr:pos x="285750" y="10915650"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1059,7 +1427,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. ตรวจก่อนไปต่อ</a:t>
+            <a:t>1. เตรียมโค้ด</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1072,7 +1440,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้างไฟล์ค่าในเครื่อง ใส่ค่าสองตัวจากขั้น 2 แล้วสั่งตรวจ</a:t>
+            <a:t>คัดลอกโค้ดมาเป็นโปรเจกต์ใหม่ แล้วเข้าไปในโฟลเดอร์</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1085,7 +1453,7 @@
               <a:latin typeface="Consolas"/>
               <a:cs typeface="Consolas"/>
             </a:rPr>
-            <a:t>npm run setup -- --init</a:t>
+            <a:t>git clone &lt;repo&gt; ชื่อใหม่</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1098,7 +1466,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: รู้ทันทีว่าฐานข้อมูลพร้อมหรือยัง</a:t>
+            <a:t>ได้: โฟลเดอร์ที่มีไฟล์ครบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1106,7 +1474,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="11620500"/>
+    <xdr:pos x="2286000" y="11944350"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1141,7 +1509,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="11868150"/>
+    <xdr:pos x="285750" y="12192000"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1178,7 +1546,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. ขึ้น GitHub</a:t>
+            <a:t>2. Supabase (ทำบนเว็บ)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1191,33 +1559,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้าง repo ตั้งเป็น Private แล้ว push โค้ดขึ้นไป</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5B21B6"/>
-              </a:solidFill>
-              <a:latin typeface="Consolas"/>
-              <a:cs typeface="Consolas"/>
-            </a:rPr>
-            <a:t>git add -A &amp;&amp; git commit -m "เริ่ม" &amp;&amp; git push</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ที่อยู่ repo ให้ Vercel ไปอ่าน</a:t>
+            <a:t>สร้างโปรเจกต์ Region สิงคโปร์ · SQL Editor วาง schema.sql ทั้งไฟล์ กด Run · Add user</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ตอนสร้างผู้ใช้ ต้องติ๊ก Auto Confirm User</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1225,7 +1580,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="12896850"/>
+    <xdr:pos x="2286000" y="13220700"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1260,7 +1615,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="13144500"/>
+    <xdr:pos x="285750" y="13468350"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1297,7 +1652,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. Vercel (ทำบนเว็บ)</a:t>
+            <a:t>3. ตรวจก่อนไปต่อ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1310,20 +1665,33 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Add New Project เลือก repo · ใส่ค่าสองตัว ติ๊กครบ 3 environment · Deploy</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ใส่ค่าแล้วต้องกด Redeploy หนึ่งครั้ง</a:t>
+            <a:t>สร้างไฟล์ค่าในเครื่อง ใส่ค่าสองตัวจากขั้น 2 แล้วสั่งตรวจ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run setup -- --init</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: รู้ทันทีว่าฐานข้อมูลพร้อมหรือยัง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1331,11 +1699,236 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="3200400"/>
+    <xdr:pos x="2286000" y="14497050"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="รูป 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="14744700"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="รูป 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>4. ขึ้น GitHub</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>สร้าง repo ตั้งเป็น Private แล้ว push โค้ดขึ้นไป</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git add -A &amp;&amp; git commit -m "เริ่ม" &amp;&amp; git push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ที่อยู่ repo ให้ Vercel ไปอ่าน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2286000" y="15773400"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="รูป 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="16021050"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="รูป 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>5. Vercel (ทำบนเว็บ)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Add New Project เลือก repo · ใส่ค่าสองตัว ติ๊กครบ 3 environment · Deploy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ค่าแล้วต้องกด Redeploy หนึ่งครั้ง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="6076950"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="รูป 22"/>
+        <xdr:cNvPr id="26" name="รูป 26"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1385,232 +1978,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="3638550"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="รูป 23"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FBF0E0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ต้นทาง: Supabase</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>Project Settings &gt; API · คัดลอก Project URL และ anon public key</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ห้ามหยิบ service_role มาใส่แทน anon key</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="4667250"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="รูป 24"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="B26A00"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="4914900"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="รูป 25"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FBF0E0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ปลายทาง 1: ไฟล์ .env.local</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไฟล์ในเครื่องตัวเอง ใช้ตอนรันในเครื่อง</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5B21B6"/>
-              </a:solidFill>
-              <a:latin typeface="Consolas"/>
-              <a:cs typeface="Consolas"/>
-            </a:rPr>
-            <a:t>npm run setup -- --init</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไฟล์นี้ต้องไม่ขึ้น git เด็ดขาด</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="5943600"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="รูป 26"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="B26A00"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="6191250"/>
+    <xdr:pos x="4857750" y="6515100"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1647,7 +2015,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ปลายทาง 2: Vercel</a:t>
+            <a:t>ต้นทาง: Supabase</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1660,7 +2028,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Environment Variables · ติ๊กครบ Production, Preview, Development</a:t>
+            <a:t>Project Settings &gt; API · คัดลอก Project URL และ anon public key</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1673,7 +2041,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ใส่ที่เครื่องอย่างเดียว เว็บจริงยังล็อกอินไม่ได้</a:t>
+            <a:t>ห้ามหยิบ service_role มาใส่แทน anon key</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1681,7 +2049,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="7219950"/>
+    <xdr:pos x="6858000" y="7543800"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1716,7 +2084,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="7467600"/>
+    <xdr:pos x="4857750" y="7791450"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1753,7 +2121,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>กด Redeploy หนึ่งครั้ง</a:t>
+            <a:t>ปลายทาง 1: ไฟล์ .env.local</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1766,20 +2134,33 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Vercel &gt; Deployments &gt; Redeploy</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="8A5200"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ค่าถูกฝังลงไฟล์ที่เบราว์เซอร์โหลด</a:t>
+            <a:t>ไฟล์ในเครื่องตัวเอง ใช้ตอนรันในเครื่อง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run setup -- --init</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไฟล์นี้ต้องไม่ขึ้น git เด็ดขาด</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1787,11 +2168,223 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="8877300"/>
+    <xdr:pos x="6858000" y="8820150"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="รูป 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="B26A00"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="9067800"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="รูป 31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ปลายทาง 2: Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Environment Variables · ติ๊กครบ Production, Preview, Development</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ที่เครื่องอย่างเดียว เว็บจริงยังล็อกอินไม่ได้</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6858000" y="10096500"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="รูป 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="B26A00"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="10344150"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="รูป 33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>กด Redeploy หนึ่งครั้ง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel &gt; Deployments &gt; Redeploy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="8A5200"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ค่าถูกฝังลงไฟล์ที่เบราว์เซอร์โหลด</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="11753850"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="รูป 30"/>
+        <xdr:cNvPr id="34" name="รูป 34"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1841,219 +2434,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="9315450"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="รูป 31"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="E7F0FA"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. ซื้อ 1 ใบ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หน้าซื้อสินค้าและบริการ บันทึกใบซื้อทดลอง</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="0B5FA5"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ของเข้าคลัง ยอดคงเหลือเพิ่ม</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="10344150"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="รูป 32"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="0B5FA5"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="10591800"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="รูป 33"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="E7F0FA"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>2. ตรวจยอดคงเหลือ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หน้าข้อมูลสินค้า ดูรายคลังรายช่องเก็บ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="0B5FA5"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ยืนยันว่าของเข้าถูกที่</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="11620500"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="รูป 34"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="0B5FA5"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="11868150"/>
+    <xdr:pos x="4857750" y="12192000"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2090,7 +2471,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. ขาย POS 1 บิล</a:t>
+            <a:t>1. ซื้อ 1 ใบ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2103,7 +2484,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ยิงบาร์โค๊ด คิดเงิน พิมพ์ใบเสร็จ</a:t>
+            <a:t>หน้าซื้อสินค้าและบริการ บันทึกใบซื้อทดลอง</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2116,7 +2497,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ยอดคงเหลือลดลงตามจริง</a:t>
+            <a:t>ได้: ของเข้าคลัง ยอดคงเหลือเพิ่ม</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2124,7 +2505,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="12896850"/>
+    <xdr:pos x="6858000" y="13220700"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2159,7 +2540,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="13144500"/>
+    <xdr:pos x="4857750" y="13468350"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2196,7 +2577,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. ออกใบกำกับภาษี 1 ใบ</a:t>
+            <a:t>2. ตรวจยอดคงเหลือ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2209,20 +2590,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ตรวจหัวเอกสารว่าชื่อกิจการและเลขผู้เสียภาษีถูก</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หัวเอกสารผิด = ยังไม่ได้ตั้งข้อมูลกิจการ</a:t>
+            <a:t>หน้าข้อมูลสินค้า ดูรายคลังรายช่องเก็บ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยืนยันว่าของเข้าถูกที่</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2230,7 +2611,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="14173200"/>
+    <xdr:pos x="6858000" y="14497050"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2265,7 +2646,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="14420850"/>
+    <xdr:pos x="4857750" y="14744700"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2302,7 +2683,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. ดูรายงานว่ายอดตรง</a:t>
+            <a:t>3. ขาย POS 1 บิล</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2315,7 +2696,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เทียบกับที่ทดลองทำไปทุกใบ</a:t>
+            <a:t>ยิงบาร์โค๊ด คิดเงิน พิมพ์ใบเสร็จ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2328,7 +2709,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ยืนยันว่าตัวเลขเชื่อได้</a:t>
+            <a:t>ได้: ยอดคงเหลือลดลงตามจริง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2336,7 +2717,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="15449550"/>
+    <xdr:pos x="6858000" y="15773400"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2371,7 +2752,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="15697200"/>
+    <xdr:pos x="4857750" y="16021050"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2408,7 +2789,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>6. สำรอง แล้วทดลองกู้คืน</a:t>
+            <a:t>4. ออกใบกำกับภาษี 1 ใบ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2421,7 +2802,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>หน้าสำรองข้อมูล ดาวน์โหลดไฟล์ แล้วกู้คืนกลับจริง ๆ</a:t>
+            <a:t>ตรวจหัวเอกสารว่าชื่อกิจการและเลขผู้เสียภาษีถูก</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2434,7 +2815,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ห้ามข้าม ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง</a:t>
+            <a:t>หัวเอกสารผิด = ยังไม่ได้ตั้งข้อมูลกิจการ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2442,7 +2823,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="16725900"/>
+    <xdr:pos x="6858000" y="17049750"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2477,7 +2858,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="16973550"/>
+    <xdr:pos x="4857750" y="17297400"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2514,7 +2895,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>7. ล้างข้อมูลทดลอง</a:t>
+            <a:t>5. ดูรายงานว่ายอดตรง</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2527,20 +2908,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ลบเอกสารทดลองทั้งหมด แล้วใส่ยอดยกมาจริง</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไม่ล้าง รายงานเดือนแรกจะมีตัวเลขทดลองปน</a:t>
+            <a:t>เทียบกับที่ทดลองทำไปทุกใบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยืนยันว่าตัวเลขเชื่อได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2548,11 +2929,223 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="3200400"/>
+    <xdr:pos x="6858000" y="18326100"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="รูป 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="18573750"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="รูป 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>6. สำรอง แล้วทดลองกู้คืน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หน้าสำรองข้อมูล ดาวน์โหลดไฟล์ แล้วกู้คืนกลับจริง ๆ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ห้ามข้าม ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6858000" y="19602450"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="รูป 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="19850100"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="รูป 47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>7. ล้างข้อมูลทดลอง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบเอกสารทดลองทั้งหมด แล้วใส่ยอดยกมาจริง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่ล้าง รายงานเดือนแรกจะมีตัวเลขทดลองปน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="6076950"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="รูป 44"/>
+        <xdr:cNvPr id="48" name="รูป 48"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2602,219 +3195,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="3638550"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="รูป 45"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. ข้อมูลกิจการ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ชื่อ ที่อยู่ เลขประจำตัวผู้เสียภาษี 13 หลัก สาขา</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ต้องมีก่อนออกเอกสารใบแรก</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="4667250"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="รูป 46"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="4914900"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="รูป 47"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>2. กลุ่มเอกสาร</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>รูปแบบเลขที่ เช่น IV-202609-0001</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เปลี่ยนทีหลัง เลขเก่าไม่เปลี่ยนตาม</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="5943600"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="รูป 48"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="6191250"/>
+    <xdr:pos x="9429750" y="6515100"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2851,7 +3232,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. คลังและที่เก็บ</a:t>
+            <a:t>1. ข้อมูลกิจการ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2864,7 +3245,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เพิ่มคลัง แล้วเพิ่มช่องเก็บในแต่ละคลัง</a:t>
+            <a:t>ชื่อ ที่อยู่ เลขประจำตัวผู้เสียภาษี 13 หลัก สาขา</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2877,7 +3258,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ไม่มีคลัง รับสินค้าเข้าไม่ได้เลย</a:t>
+            <a:t>ต้องมีก่อนออกเอกสารใบแรก</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2885,7 +3266,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="7219950"/>
+    <xdr:pos x="11430000" y="7543800"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2920,7 +3301,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="7467600"/>
+    <xdr:pos x="9429750" y="7791450"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2957,7 +3338,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. กลุ่ม ยี่ห้อ ประเภทสินค้า</a:t>
+            <a:t>2. กลุ่มเอกสาร</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2970,20 +3351,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ทะเบียนสามมิติสำหรับจำแนกสินค้า</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: รายการให้เลือกตอนเพิ่มสินค้า</a:t>
+            <a:t>รูปแบบเลขที่ เช่น IV-202609-0001</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เปลี่ยนทีหลัง เลขเก่าไม่เปลี่ยนตาม</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2991,7 +3372,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="8496300"/>
+    <xdr:pos x="11430000" y="8820150"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3026,7 +3407,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="8743950"/>
+    <xdr:pos x="9429750" y="9067800"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3063,7 +3444,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. ข้อมูลสินค้า</a:t>
+            <a:t>3. คลังและที่เก็บ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3076,20 +3457,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัส ชื่อ หน่วยนับ ราคา บาร์โค๊ด · นำเข้าจาก Excel ได้ถ้ามีเยอะ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: แกนของทั้งระบบ</a:t>
+            <a:t>เพิ่มคลัง แล้วเพิ่มช่องเก็บในแต่ละคลัง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่มีคลัง รับสินค้าเข้าไม่ได้เลย</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3097,7 +3478,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="9772650"/>
+    <xdr:pos x="11430000" y="10096500"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3132,7 +3513,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="10020300"/>
+    <xdr:pos x="9429750" y="10344150"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3169,7 +3550,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>6. ยอดยกมา</a:t>
+            <a:t>4. กลุ่ม ยี่ห้อ ประเภทสินค้า</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3182,20 +3563,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รับสินค้าเข้าครั้งแรก หรือใช้ใบตรวจนับ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไม่ใส่ ระบบคิดว่าไม่มีของ แล้วขายไม่ได้</a:t>
+            <a:t>ทะเบียนสามมิติสำหรับจำแนกสินค้า</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: รายการให้เลือกตอนเพิ่มสินค้า</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3203,7 +3584,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="11049000"/>
+    <xdr:pos x="11430000" y="11372850"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3238,7 +3619,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="11296650"/>
+    <xdr:pos x="9429750" y="11620500"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3275,7 +3656,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>7. ทะเบียนลูกค้าและเจ้าหนี้</a:t>
+            <a:t>5. ข้อมูลสินค้า</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3288,7 +3669,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัส ชื่อ ที่อยู่แยกช่อง เลขผู้เสียภาษี</a:t>
+            <a:t>รหัส ชื่อ หน่วยนับ ราคา บาร์โค๊ด · นำเข้าจาก Excel ได้ถ้ามีเยอะ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3301,7 +3682,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ข้อมูลผู้ซื้อผู้ขายบนเอกสาร</a:t>
+            <a:t>ได้: แกนของทั้งระบบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3309,7 +3690,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="12325350"/>
+    <xdr:pos x="11430000" y="12649200"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3344,7 +3725,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="12573000"/>
+    <xdr:pos x="9429750" y="12896850"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3381,7 +3762,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>8. พนักงานขาย</a:t>
+            <a:t>6. ยอดยกมา</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3394,20 +3775,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัสและชื่อพนักงานขายทุกคน</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ดูยอดขายรายคนและตั้งเป้ารายคนได้</a:t>
+            <a:t>รับสินค้าเข้าครั้งแรก หรือใช้ใบตรวจนับ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่ใส่ ระบบคิดว่าไม่มีของ แล้วขายไม่ได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3415,7 +3796,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="13601700"/>
+    <xdr:pos x="11430000" y="13925550"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3450,7 +3831,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="13849350"/>
+    <xdr:pos x="9429750" y="14173200"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3487,7 +3868,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>9. ผู้ใช้งานที่เหลือ</a:t>
+            <a:t>7. ทะเบียนลูกค้าและเจ้าหนี้</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3500,20 +3881,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หนึ่งคนหนึ่งบัญชี ห้ามใช้ร่วมกัน</a:t>
+            <a:t>รหัส ชื่อ ที่อยู่แยกช่อง เลขผู้เสียภาษี</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ข้อมูลผู้ซื้อผู้ขายบนเอกสาร</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3521,7 +3902,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="14878050"/>
+    <xdr:pos x="11430000" y="15201900"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3556,7 +3937,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="15125700"/>
+    <xdr:pos x="9429750" y="15449550"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3593,7 +3974,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>10. สิทธิการใช้งานรายคน</a:t>
+            <a:t>8. พนักงานขาย</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3606,20 +3987,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เลือกผู้ใช้ทีละคน ติ๊กว่าเห็นหน้าจอไหนและแก้ไขได้ไหม</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>คุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล (ดูชีต 8)</a:t>
+            <a:t>รหัสและชื่อพนักงานขายทุกคน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ดูยอดขายรายคนและตั้งเป้ารายคนได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3627,11 +4008,223 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="18383250"/>
+    <xdr:pos x="11430000" y="16478250"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="รูป 64"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="16725900"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="รูป 65"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>9. ผู้ใช้งานที่เหลือ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หนึ่งคนหนึ่งบัญชี ห้ามใช้ร่วมกัน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="11430000" y="17754600"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="รูป 66"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="18002250"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="67" name="รูป 67"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>10. สิทธิการใช้งานรายคน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เลือกผู้ใช้ทีละคน ติ๊กว่าเห็นหน้าจอไหนและแก้ไขได้ไหม</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>คุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล (ดูชีต 8)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="21259800"/>
     <xdr:ext cx="4762500" cy="247650"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="64" name="รูป 64"/>
+        <xdr:cNvPr id="68" name="รูป 68"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3668,11 +4261,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="18688050"/>
+    <xdr:pos x="285750" y="21564600"/>
     <xdr:ext cx="4191000" cy="1676400"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="65" name="รูป 65"/>
+        <xdr:cNvPr id="69" name="รูป 69"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3817,11 +4410,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="18688050"/>
+    <xdr:pos x="4762500" y="21564600"/>
     <xdr:ext cx="4191000" cy="1676400"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="66" name="รูป 66"/>
+        <xdr:cNvPr id="70" name="รูป 70"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3966,11 +4559,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="18688050"/>
+    <xdr:pos x="9239250" y="21564600"/>
     <xdr:ext cx="4191000" cy="1676400"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="67" name="รูป 67"/>
+        <xdr:cNvPr id="71" name="รูป 71"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4115,11 +4708,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="20745450"/>
+    <xdr:pos x="285750" y="23622000"/>
     <xdr:ext cx="2857500" cy="228600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="68" name="รูป 68"/>
+        <xdr:cNvPr id="72" name="รูป 72"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4156,11 +4749,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="21031200"/>
+    <xdr:pos x="285750" y="23907750"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="69" name="รูป 69"/>
+        <xdr:cNvPr id="73" name="รูป 73"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4201,11 +4794,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="3619500" y="21031200"/>
+    <xdr:pos x="3619500" y="23907750"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="70" name="รูป 70"/>
+        <xdr:cNvPr id="74" name="รูป 74"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4246,11 +4839,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6953250" y="21031200"/>
+    <xdr:pos x="6953250" y="23907750"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="71" name="รูป 71"/>
+        <xdr:cNvPr id="75" name="รูป 75"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4291,11 +4884,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="10287000" y="21031200"/>
+    <xdr:pos x="10287000" y="23907750"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="72" name="รูป 72"/>
+        <xdr:cNvPr id="76" name="รูป 76"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4523,7 +5116,7 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFAU 3.3 · รอบ 99 (2026-09-12)</t>
+          <t xml:space="preserve">OFAU 3.3 · รอบ 100 (2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -5856,7 +6449,7 @@
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 99 (2026-09-12))</t>
+          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 100 (2026-09-12))</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="2">

--- a/Docs/เช็คลิสต์การติดตั้ง.xlsx
+++ b/Docs/เช็คลิสต์การติดตั้ง.xlsx
@@ -954,11 +954,814 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="5543550"/>
+    <xdr:pos x="285750" y="5524500"/>
+    <xdr:ext cx="13335000" cy="247650"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="รูป 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1250" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หน้าเว็บที่ต้องเข้าไปทำ — เส้นทางการกดทีละขั้น (เรียงตามลำดับที่ต้องทำ ไม่ใช่ตามลำดับเมนูบนหน้าจอ)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="5829300"/>
+    <xdr:ext cx="4191000" cy="4000500"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="รูป 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1300" b="1">
+              <a:solidFill>
+                <a:srgbClr val="8A978F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>GitHub</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>github.com</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="8A978F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>1. มุมขวาบน เครื่องหมาย + &gt; New repository</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ตั้งชื่อ repo · เลือก Private · ไม่ต้องติ๊ก Add a README · กด Create repository</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ได้: ที่อยู่ repo ที่ขึ้นมาในหน้าถัดไป คัดลอกเก็บไว้</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="8A978F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>2. หน้า repo &gt; ดูรายการไฟล์ในหน้าแรก</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ไล่ดูว่ามีไฟล์อะไรขึ้นไปบ้าง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ต้องไม่เห็นไฟล์ .env.local ถ้าเห็น ให้ไปสร้าง anon key ใหม่ทันที</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="8A978F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>3. Settings &gt; Collaborators (ถ้าทำงานหลายคน)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    เชิญเพื่อนร่วมงานด้วยบัญชี GitHub ของเขา</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ได้: คนอื่น push โค้ดขึ้น repo เดียวกันได้</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="5829300"/>
+    <xdr:ext cx="4191000" cy="4000500"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="รูป 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1300" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>vercel.com</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>1. หน้าแรก &gt; Add New &gt; Project</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    หา repo ที่เพิ่ง push แล้วกด Import · Framework ขึ้น Next.js เอง ไม่ต้องแก้ · Root Directory ปล่อยเป็น ./</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ได้: โปรเจกต์ที่ผูกกับ repo แล้ว</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>2. Settings &gt; Environment Variables</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ช่อง Key ใส่ NEXT_PUBLIC_SUPABASE_URL · ช่อง Value วางค่าที่คัดลอกมา · ติ๊กครบ Production, Preview, Development · Save</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ทำซ้ำอีกรอบกับ NEXT_PUBLIC_SUPABASE_ANON_KEY</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>3. Deployments &gt; จุดสามจุดของรายการบนสุด &gt; Redeploy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    กดยืนยัน ไม่ต้องติ๊ก Use existing Build Cache · รอจนสถานะขึ้น Ready</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ไม่กดขั้นนี้ ค่าที่เพิ่งใส่จะยังไม่มีผล</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>4. Settings &gt; Domains (เฉพาะถ้าใช้โดเมนของตัวเอง)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ใส่ชื่อโดเมน แล้วทำตามที่ Vercel บอกให้ตั้งค่า DNS</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ได้: เว็บเปิดด้วยโดเมนของกิจการ</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="5829300"/>
+    <xdr:ext cx="4191000" cy="4000500"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="รูป 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1300" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Supabase</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>supabase.com</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>1. Dashboard &gt; New project</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ตั้งชื่อ · ตั้ง Database Password แล้วเก็บไว้ให้ดี · Region เลือก Southeast Asia (Singapore) · รอประมาณ 2 นาที</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    Region เลือกผิดแล้วย้ายทีหลังไม่ได้ ต้องสร้างโปรเจกต์ใหม่</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>2. SQL Editor &gt; New query</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    เปิดไฟล์ supabase/schema.sql คัดลอกทั้งไฟล์ วางลงไป แล้วกด Run (หรือ Ctrl+Enter)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ท้ายผลลัพธ์ต้องมีตารางสรุป ขึ้น ผ่าน ครบทุกแถว</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>3. Authentication &gt; Users &gt; Add user &gt; Create new user</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    กรอกอีเมลและรหัสผ่าน แล้วติ๊ก Auto Confirm User ก่อนกดสร้าง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ไม่ติ๊ก จะล็อกอินไม่ได้เลย แก้ทีหลังได้ที่ผู้ใช้คนนั้น &gt; Confirm email</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>4. Authentication &gt; Sign In / Providers &gt; Email</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ปิด Confirm email · เปิด Allow new users to sign up ชั่วคราวถ้าจะเพิ่มผู้ใช้จากในโปรแกรม</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    เพิ่มผู้ใช้ครบแล้วให้กลับมาปิด Allow new users to sign up</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>5. Project Settings &gt; API</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    คัดลอก Project URL และ Project API keys &gt; anon public (ตัวที่เขียนว่า public เท่านั้น)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    service_role ที่อยู่หน้าเดียวกัน ใช้เฉพาะงานไลน์ ห้ามใส่ช่อง anon</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>6. Project Settings &gt; General</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ดูสถานะโปรเจกต์ · ถ้าขึ้นว่า Paused ให้กด Restore</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    โปรเจกต์ฟรีที่ไม่มีคนใช้เกิน 7 วันจะถูก pause เอง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>7. Table Editor (ไว้ดูข้อมูลจริง)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    เลือกตารางทางซ้าย แล้วดูข้อมูลในตารางนั้นได้เลย</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>    ได้: ใช้ไล่หาสาเหตุว่าข้อมูลเข้าไปจริงหรือไม่</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="9772650"/>
     <xdr:ext cx="13335000" cy="342900"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="รูป 9"/>
+        <xdr:cNvPr id="13" name="รูป 13"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -999,11 +1802,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="6076950"/>
+    <xdr:pos x="285750" y="10306050"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="รูป 10"/>
+        <xdr:cNvPr id="14" name="รูป 14"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1053,219 +1856,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="6515100"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="รูป 11"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EFF1F0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ผู้ใช้ (เบราว์เซอร์)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เปิดเว็บตามที่อยู่ของ Vercel</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B756F"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: หน้าเว็บของระบบ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="7543800"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="รูป 12"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="8A978F"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="7791450"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="รูป 13"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EFF1F0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>Vercel — ที่รันเว็บ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="3A423D"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เอาโค้ดจาก GitHub มารันเอง ทุกครั้งที่ push</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="6B756F"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เก็บเฉพาะโค้ด ไม่มีข้อมูลของกิจการอยู่เลย</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="8820150"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="รูป 14"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="8A978F"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="8A978F"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="9067800"/>
+    <xdr:pos x="285750" y="10744200"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1302,7 +1893,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Supabase — ฐานข้อมูล + ล็อกอิน</a:t>
+            <a:t>ผู้ใช้ (เบราว์เซอร์)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1315,20 +1906,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เก็บข้อมูลจริงทั้งหมด และตรวจรหัสผ่านตอนล็อกอิน</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ลบโปรเจกต์นี้เมื่อไร ข้อมูลหายทั้งหมดทันที</a:t>
+            <a:t>เปิดเว็บตามที่อยู่ของ Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: หน้าเว็บของระบบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1336,11 +1927,223 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="10477500"/>
+    <xdr:pos x="2286000" y="11772900"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="รูป 16"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8A978F"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="12020550"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="รูป 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel — ที่รันเว็บ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เอาโค้ดจาก GitHub มารันเอง ทุกครั้งที่ push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="6B756F"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บเฉพาะโค้ด ไม่มีข้อมูลของกิจการอยู่เลย</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2286000" y="13049250"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="รูป 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="8A978F"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="13296900"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="รูป 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFF1F0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="8A978F"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Supabase — ฐานข้อมูล + ล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="3A423D"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เก็บข้อมูลจริงทั้งหมด และตรวจรหัสผ่านตอนล็อกอิน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบโปรเจกต์นี้เมื่อไร ข้อมูลหายทั้งหมดทันที</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="14706600"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="รูป 16"/>
+        <xdr:cNvPr id="20" name="รูป 20"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1390,232 +2193,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="10915650"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="รูป 17"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. เตรียมโค้ด</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>คัดลอกโค้ดมาเป็นโปรเจกต์ใหม่ แล้วเข้าไปในโฟลเดอร์</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5B21B6"/>
-              </a:solidFill>
-              <a:latin typeface="Consolas"/>
-              <a:cs typeface="Consolas"/>
-            </a:rPr>
-            <a:t>git clone &lt;repo&gt; ชื่อใหม่</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: โฟลเดอร์ที่มีไฟล์ครบ</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="11944350"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="รูป 18"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="12192000"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="รูป 19"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>2. Supabase (ทำบนเว็บ)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>สร้างโปรเจกต์ Region สิงคโปร์ · SQL Editor วาง schema.sql ทั้งไฟล์ กด Run · Add user</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ตอนสร้างผู้ใช้ ต้องติ๊ก Auto Confirm User</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="13220700"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="รูป 20"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="13468350"/>
+    <xdr:pos x="285750" y="15144750"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1652,7 +2230,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. ตรวจก่อนไปต่อ</a:t>
+            <a:t>1. เตรียมโค้ด</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1665,7 +2243,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้างไฟล์ค่าในเครื่อง ใส่ค่าสองตัวจากขั้น 2 แล้วสั่งตรวจ</a:t>
+            <a:t>คัดลอกโค้ดมาเป็นโปรเจกต์ใหม่ แล้วเข้าไปในโฟลเดอร์</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1678,7 +2256,7 @@
               <a:latin typeface="Consolas"/>
               <a:cs typeface="Consolas"/>
             </a:rPr>
-            <a:t>npm run setup -- --init</a:t>
+            <a:t>git clone &lt;repo&gt; ชื่อใหม่</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1691,7 +2269,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: รู้ทันทีว่าฐานข้อมูลพร้อมหรือยัง</a:t>
+            <a:t>ได้: โฟลเดอร์ที่มีไฟล์ครบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1699,7 +2277,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="14497050"/>
+    <xdr:pos x="2286000" y="16173450"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1734,7 +2312,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="14744700"/>
+    <xdr:pos x="285750" y="16421100"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1771,7 +2349,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. ขึ้น GitHub</a:t>
+            <a:t>2. Supabase (ทำบนเว็บ)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1784,33 +2362,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้าง repo ตั้งเป็น Private แล้ว push โค้ดขึ้นไป</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5B21B6"/>
-              </a:solidFill>
-              <a:latin typeface="Consolas"/>
-              <a:cs typeface="Consolas"/>
-            </a:rPr>
-            <a:t>git add -A &amp;&amp; git commit -m "เริ่ม" &amp;&amp; git push</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ที่อยู่ repo ให้ Vercel ไปอ่าน</a:t>
+            <a:t>สร้างโปรเจกต์ Region สิงคโปร์ · SQL Editor วาง schema.sql ทั้งไฟล์ กด Run · Add user</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ตอนสร้างผู้ใช้ ต้องติ๊ก Auto Confirm User</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1818,7 +2383,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="2286000" y="15773400"/>
+    <xdr:pos x="2286000" y="17449800"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1853,7 +2418,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="16021050"/>
+    <xdr:pos x="285750" y="17697450"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1890,7 +2455,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. Vercel (ทำบนเว็บ)</a:t>
+            <a:t>3. ตรวจก่อนไปต่อ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -1903,20 +2468,33 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Add New Project เลือก repo · ใส่ค่าสองตัว ติ๊กครบ 3 environment · Deploy</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ใส่ค่าแล้วต้องกด Redeploy หนึ่งครั้ง</a:t>
+            <a:t>สร้างไฟล์ค่าในเครื่อง ใส่ค่าสองตัวจากขั้น 2 แล้วสั่งตรวจ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run setup -- --init</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: รู้ทันทีว่าฐานข้อมูลพร้อมหรือยัง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1924,11 +2502,236 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="6076950"/>
+    <xdr:pos x="2286000" y="18726150"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="รูป 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="18973800"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="รูป 27"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>4. ขึ้น GitHub</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>สร้าง repo ตั้งเป็น Private แล้ว push โค้ดขึ้นไป</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>git add -A &amp;&amp; git commit -m "เริ่ม" &amp;&amp; git push</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ที่อยู่ repo ให้ Vercel ไปอ่าน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="2286000" y="20002500"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="รูป 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="20250150"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="รูป 29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>5. Vercel (ทำบนเว็บ)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Add New Project เลือก repo · ใส่ค่าสองตัว ติ๊กครบ 3 environment · Deploy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ค่าแล้วต้องกด Redeploy หนึ่งครั้ง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="10306050"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="รูป 26"/>
+        <xdr:cNvPr id="30" name="รูป 30"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1978,232 +2781,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="6515100"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="รูป 27"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FBF0E0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ต้นทาง: Supabase</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>Project Settings &gt; API · คัดลอก Project URL และ anon public key</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ห้ามหยิบ service_role มาใส่แทน anon key</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="7543800"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="รูป 28"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="B26A00"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="7791450"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="รูป 29"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FBF0E0"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ปลายทาง 1: ไฟล์ .env.local</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5A3600"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไฟล์ในเครื่องตัวเอง ใช้ตอนรันในเครื่อง</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="5B21B6"/>
-              </a:solidFill>
-              <a:latin typeface="Consolas"/>
-              <a:cs typeface="Consolas"/>
-            </a:rPr>
-            <a:t>npm run setup -- --init</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไฟล์นี้ต้องไม่ขึ้น git เด็ดขาด</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="8820150"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="รูป 30"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="B26A00"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="B26A00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="9067800"/>
+    <xdr:pos x="4857750" y="10744200"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2240,7 +2818,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ปลายทาง 2: Vercel</a:t>
+            <a:t>ต้นทาง: Supabase</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2253,7 +2831,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Environment Variables · ติ๊กครบ Production, Preview, Development</a:t>
+            <a:t>Project Settings &gt; API · คัดลอก Project URL และ anon public key</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2266,7 +2844,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ใส่ที่เครื่องอย่างเดียว เว็บจริงยังล็อกอินไม่ได้</a:t>
+            <a:t>ห้ามหยิบ service_role มาใส่แทน anon key</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2274,7 +2852,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="10096500"/>
+    <xdr:pos x="6858000" y="11772900"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2309,7 +2887,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="10344150"/>
+    <xdr:pos x="4857750" y="12020550"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2346,7 +2924,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>กด Redeploy หนึ่งครั้ง</a:t>
+            <a:t>ปลายทาง 1: ไฟล์ .env.local</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2359,20 +2937,33 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>Vercel &gt; Deployments &gt; Redeploy</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="8A5200"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ค่าถูกฝังลงไฟล์ที่เบราว์เซอร์โหลด</a:t>
+            <a:t>ไฟล์ในเครื่องตัวเอง ใช้ตอนรันในเครื่อง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5B21B6"/>
+              </a:solidFill>
+              <a:latin typeface="Consolas"/>
+              <a:cs typeface="Consolas"/>
+            </a:rPr>
+            <a:t>npm run setup -- --init</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไฟล์นี้ต้องไม่ขึ้น git เด็ดขาด</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2380,11 +2971,223 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="11753850"/>
+    <xdr:pos x="6858000" y="13049250"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="รูป 34"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="B26A00"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="13296900"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="รูป 35"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ปลายทาง 2: Vercel</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Environment Variables · ติ๊กครบ Production, Preview, Development</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ใส่ที่เครื่องอย่างเดียว เว็บจริงยังล็อกอินไม่ได้</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6858000" y="14325600"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="รูป 36"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="B26A00"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="14573250"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="รูป 37"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FBF0E0"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="B26A00"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>กด Redeploy หนึ่งครั้ง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="5A3600"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>Vercel &gt; Deployments &gt; Redeploy</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="8A5200"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ค่าถูกฝังลงไฟล์ที่เบราว์เซอร์โหลด</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="15982950"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="รูป 34"/>
+        <xdr:cNvPr id="38" name="รูป 38"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2434,219 +3237,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="12192000"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="รูป 35"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="E7F0FA"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. ซื้อ 1 ใบ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หน้าซื้อสินค้าและบริการ บันทึกใบซื้อทดลอง</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="0B5FA5"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ของเข้าคลัง ยอดคงเหลือเพิ่ม</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="13220700"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="รูป 36"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="0B5FA5"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="13468350"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="รูป 37"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="E7F0FA"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>2. ตรวจยอดคงเหลือ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="0A3358"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หน้าข้อมูลสินค้า ดูรายคลังรายช่องเก็บ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="0B5FA5"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ยืนยันว่าของเข้าถูกที่</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="14497050"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="รูป 38"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="0B5FA5"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="0B5FA5"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="14744700"/>
+    <xdr:pos x="4857750" y="16421100"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2683,7 +3274,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. ขาย POS 1 บิล</a:t>
+            <a:t>1. ซื้อ 1 ใบ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2696,7 +3287,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ยิงบาร์โค๊ด คิดเงิน พิมพ์ใบเสร็จ</a:t>
+            <a:t>หน้าซื้อสินค้าและบริการ บันทึกใบซื้อทดลอง</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2709,7 +3300,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ยอดคงเหลือลดลงตามจริง</a:t>
+            <a:t>ได้: ของเข้าคลัง ยอดคงเหลือเพิ่ม</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2717,7 +3308,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="15773400"/>
+    <xdr:pos x="6858000" y="17449800"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2752,7 +3343,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="16021050"/>
+    <xdr:pos x="4857750" y="17697450"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2789,7 +3380,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. ออกใบกำกับภาษี 1 ใบ</a:t>
+            <a:t>2. ตรวจยอดคงเหลือ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2802,20 +3393,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ตรวจหัวเอกสารว่าชื่อกิจการและเลขผู้เสียภาษีถูก</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หัวเอกสารผิด = ยังไม่ได้ตั้งข้อมูลกิจการ</a:t>
+            <a:t>หน้าข้อมูลสินค้า ดูรายคลังรายช่องเก็บ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยืนยันว่าของเข้าถูกที่</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2823,7 +3414,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="17049750"/>
+    <xdr:pos x="6858000" y="18726150"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2858,7 +3449,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="17297400"/>
+    <xdr:pos x="4857750" y="18973800"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2895,7 +3486,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. ดูรายงานว่ายอดตรง</a:t>
+            <a:t>3. ขาย POS 1 บิล</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2908,7 +3499,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เทียบกับที่ทดลองทำไปทุกใบ</a:t>
+            <a:t>ยิงบาร์โค๊ด คิดเงิน พิมพ์ใบเสร็จ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -2921,7 +3512,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ยืนยันว่าตัวเลขเชื่อได้</a:t>
+            <a:t>ได้: ยอดคงเหลือลดลงตามจริง</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2929,7 +3520,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="18326100"/>
+    <xdr:pos x="6858000" y="20002500"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2964,7 +3555,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="18573750"/>
+    <xdr:pos x="4857750" y="20250150"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3001,7 +3592,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>6. สำรอง แล้วทดลองกู้คืน</a:t>
+            <a:t>4. ออกใบกำกับภาษี 1 ใบ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3014,7 +3605,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>หน้าสำรองข้อมูล ดาวน์โหลดไฟล์ แล้วกู้คืนกลับจริง ๆ</a:t>
+            <a:t>ตรวจหัวเอกสารว่าชื่อกิจการและเลขผู้เสียภาษีถูก</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3027,7 +3618,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ห้ามข้าม ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง</a:t>
+            <a:t>หัวเอกสารผิด = ยังไม่ได้ตั้งข้อมูลกิจการ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3035,7 +3626,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6858000" y="19602450"/>
+    <xdr:pos x="6858000" y="21278850"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3070,7 +3661,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4857750" y="19850100"/>
+    <xdr:pos x="4857750" y="21526500"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3107,7 +3698,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>7. ล้างข้อมูลทดลอง</a:t>
+            <a:t>5. ดูรายงานว่ายอดตรง</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3120,20 +3711,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ลบเอกสารทดลองทั้งหมด แล้วใส่ยอดยกมาจริง</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไม่ล้าง รายงานเดือนแรกจะมีตัวเลขทดลองปน</a:t>
+            <a:t>เทียบกับที่ทดลองทำไปทุกใบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="0B5FA5"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ยืนยันว่าตัวเลขเชื่อได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3141,11 +3732,223 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="6076950"/>
+    <xdr:pos x="6858000" y="22555200"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="รูป 48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="22802850"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="รูป 49"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>6. สำรอง แล้วทดลองกู้คืน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หน้าสำรองข้อมูล ดาวน์โหลดไฟล์ แล้วกู้คืนกลับจริง ๆ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ห้ามข้าม ไฟล์สำรองที่กู้ไม่ได้ ไม่ใช่ไฟล์สำรอง</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="6858000" y="23831550"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="รูป 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0B5FA5"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="4857750" y="24079200"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="รูป 51"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="E7F0FA"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="0B5FA5"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>7. ล้างข้อมูลทดลอง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="0A3358"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ลบเอกสารทดลองทั้งหมด แล้วใส่ยอดยกมาจริง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่ล้าง รายงานเดือนแรกจะมีตัวเลขทดลองปน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="10306050"/>
     <xdr:ext cx="4191000" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="รูป 48"/>
+        <xdr:cNvPr id="52" name="รูป 52"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3195,219 +3998,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="6515100"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="49" name="รูป 49"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>1. ข้อมูลกิจการ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ชื่อ ที่อยู่ เลขประจำตัวผู้เสียภาษี 13 หลัก สาขา</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ต้องมีก่อนออกเอกสารใบแรก</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="7543800"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="50" name="รูป 50"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="7791450"/>
-    <xdr:ext cx="4191000" cy="990600"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="รูป 51"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EAF5EF"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>2. กลุ่มเอกสาร</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="900">
-              <a:solidFill>
-                <a:srgbClr val="1B3D2A"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>รูปแบบเลขที่ เช่น IV-202609-0001</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>เปลี่ยนทีหลัง เลขเก่าไม่เปลี่ยนตาม</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="8820150"/>
-    <xdr:ext cx="190500" cy="209550"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="รูป 52"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="2E7D52"/>
-        </a:solidFill>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="2E7D52"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-  <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="9067800"/>
+    <xdr:pos x="9429750" y="10744200"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3444,7 +4035,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>3. คลังและที่เก็บ</a:t>
+            <a:t>1. ข้อมูลกิจการ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3457,7 +4048,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เพิ่มคลัง แล้วเพิ่มช่องเก็บในแต่ละคลัง</a:t>
+            <a:t>ชื่อ ที่อยู่ เลขประจำตัวผู้เสียภาษี 13 หลัก สาขา</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3470,7 +4061,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ไม่มีคลัง รับสินค้าเข้าไม่ได้เลย</a:t>
+            <a:t>ต้องมีก่อนออกเอกสารใบแรก</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3478,7 +4069,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="10096500"/>
+    <xdr:pos x="11430000" y="11772900"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3513,7 +4104,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="10344150"/>
+    <xdr:pos x="9429750" y="12020550"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3550,7 +4141,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>4. กลุ่ม ยี่ห้อ ประเภทสินค้า</a:t>
+            <a:t>2. กลุ่มเอกสาร</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3563,20 +4154,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ทะเบียนสามมิติสำหรับจำแนกสินค้า</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: รายการให้เลือกตอนเพิ่มสินค้า</a:t>
+            <a:t>รูปแบบเลขที่ เช่น IV-202609-0001</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เปลี่ยนทีหลัง เลขเก่าไม่เปลี่ยนตาม</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3584,7 +4175,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="11372850"/>
+    <xdr:pos x="11430000" y="13049250"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3619,7 +4210,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="11620500"/>
+    <xdr:pos x="9429750" y="13296900"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3656,7 +4247,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>5. ข้อมูลสินค้า</a:t>
+            <a:t>3. คลังและที่เก็บ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3669,20 +4260,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัส ชื่อ หน่วยนับ ราคา บาร์โค๊ด · นำเข้าจาก Excel ได้ถ้ามีเยอะ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: แกนของทั้งระบบ</a:t>
+            <a:t>เพิ่มคลัง แล้วเพิ่มช่องเก็บในแต่ละคลัง</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่มีคลัง รับสินค้าเข้าไม่ได้เลย</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3690,7 +4281,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="12649200"/>
+    <xdr:pos x="11430000" y="14325600"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3725,7 +4316,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="12896850"/>
+    <xdr:pos x="9429750" y="14573250"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3762,7 +4353,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>6. ยอดยกมา</a:t>
+            <a:t>4. กลุ่ม ยี่ห้อ ประเภทสินค้า</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3775,20 +4366,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รับสินค้าเข้าครั้งแรก หรือใช้ใบตรวจนับ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ไม่ใส่ ระบบคิดว่าไม่มีของ แล้วขายไม่ได้</a:t>
+            <a:t>ทะเบียนสามมิติสำหรับจำแนกสินค้า</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: รายการให้เลือกตอนเพิ่มสินค้า</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3796,7 +4387,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="13925550"/>
+    <xdr:pos x="11430000" y="15601950"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3831,7 +4422,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="14173200"/>
+    <xdr:pos x="9429750" y="15849600"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3868,7 +4459,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>7. ทะเบียนลูกค้าและเจ้าหนี้</a:t>
+            <a:t>5. ข้อมูลสินค้า</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3881,7 +4472,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัส ชื่อ ที่อยู่แยกช่อง เลขผู้เสียภาษี</a:t>
+            <a:t>รหัส ชื่อ หน่วยนับ ราคา บาร์โค๊ด · นำเข้าจาก Excel ได้ถ้ามีเยอะ</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3894,7 +4485,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>ได้: ข้อมูลผู้ซื้อผู้ขายบนเอกสาร</a:t>
+            <a:t>ได้: แกนของทั้งระบบ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -3902,7 +4493,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="15201900"/>
+    <xdr:pos x="11430000" y="16878300"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3937,7 +4528,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="15449550"/>
+    <xdr:pos x="9429750" y="17125950"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3974,7 +4565,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>8. พนักงานขาย</a:t>
+            <a:t>6. ยอดยกมา</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -3987,20 +4578,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>รหัสและชื่อพนักงานขายทุกคน</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850">
-              <a:solidFill>
-                <a:srgbClr val="2E7D52"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>ได้: ดูยอดขายรายคนและตั้งเป้ารายคนได้</a:t>
+            <a:t>รับสินค้าเข้าครั้งแรก หรือใช้ใบตรวจนับ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ไม่ใส่ ระบบคิดว่าไม่มีของ แล้วขายไม่ได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4008,7 +4599,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="16478250"/>
+    <xdr:pos x="11430000" y="18154650"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4043,7 +4634,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="16725900"/>
+    <xdr:pos x="9429750" y="18402300"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4080,7 +4671,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>9. ผู้ใช้งานที่เหลือ</a:t>
+            <a:t>7. ทะเบียนลูกค้าและเจ้าหนี้</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4093,20 +4684,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>หนึ่งคนหนึ่งบัญชี ห้ามใช้ร่วมกัน</a:t>
+            <a:t>รหัส ชื่อ ที่อยู่แยกช่อง เลขผู้เสียภาษี</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ข้อมูลผู้ซื้อผู้ขายบนเอกสาร</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4114,7 +4705,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="11430000" y="17754600"/>
+    <xdr:pos x="11430000" y="19431000"/>
     <xdr:ext cx="190500" cy="209550"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4149,7 +4740,7 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9429750" y="18002250"/>
+    <xdr:pos x="9429750" y="19678650"/>
     <xdr:ext cx="4191000" cy="990600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4186,7 +4777,7 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>10. สิทธิการใช้งานรายคน</a:t>
+            <a:t>8. พนักงานขาย</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -4199,20 +4790,20 @@
               <a:latin typeface="Tahoma"/>
               <a:cs typeface="Tahoma"/>
             </a:rPr>
-            <a:t>เลือกผู้ใช้ทีละคน ติ๊กว่าเห็นหน้าจอไหนและแก้ไขได้ไหม</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="th-TH" sz="850" b="1">
-              <a:solidFill>
-                <a:srgbClr val="B3261E"/>
-              </a:solidFill>
-              <a:latin typeface="Tahoma"/>
-              <a:cs typeface="Tahoma"/>
-            </a:rPr>
-            <a:t>คุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล (ดูชีต 8)</a:t>
+            <a:t>รหัสและชื่อพนักงานขายทุกคน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850">
+              <a:solidFill>
+                <a:srgbClr val="2E7D52"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>ได้: ดูยอดขายรายคนและตั้งเป้ารายคนได้</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4220,11 +4811,223 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="21259800"/>
+    <xdr:pos x="11430000" y="20707350"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="68" name="รูป 68"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="20955000"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="69" name="รูป 69"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>9. ผู้ใช้งานที่เหลือ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>สร้างบัญชีให้พนักงานทุกคนที่ต้องใช้ระบบ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>หนึ่งคนหนึ่งบัญชี ห้ามใช้ร่วมกัน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="11430000" y="21983700"/>
+    <xdr:ext cx="190500" cy="209550"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="70" name="รูป 70"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2E7D52"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9429750" y="22231350"/>
+    <xdr:ext cx="4191000" cy="990600"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="71" name="รูป 71"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EAF5EF"/>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:solidFill>
+            <a:srgbClr val="2E7D52"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="45720" rIns="45720" tIns="27432" bIns="27432" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>10. สิทธิการใช้งานรายคน</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="900">
+              <a:solidFill>
+                <a:srgbClr val="1B3D2A"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>เลือกผู้ใช้ทีละคน ติ๊กว่าเห็นหน้าจอไหนและแก้ไขได้ไหม</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="850" b="1">
+              <a:solidFill>
+                <a:srgbClr val="B3261E"/>
+              </a:solidFill>
+              <a:latin typeface="Tahoma"/>
+              <a:cs typeface="Tahoma"/>
+            </a:rPr>
+            <a:t>คุมลำดับงาน ไม่ใช่กำแพงกันข้อมูล (ดูชีต 8)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+  <xdr:absoluteAnchor>
+    <xdr:pos x="285750" y="25488900"/>
     <xdr:ext cx="4762500" cy="247650"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="68" name="รูป 68"/>
+        <xdr:cNvPr id="72" name="รูป 72"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4261,11 +5064,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="21564600"/>
+    <xdr:pos x="285750" y="25793700"/>
     <xdr:ext cx="4191000" cy="1676400"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="69" name="รูป 69"/>
+        <xdr:cNvPr id="73" name="รูป 73"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4410,11 +5213,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="4762500" y="21564600"/>
+    <xdr:pos x="4762500" y="25793700"/>
     <xdr:ext cx="4191000" cy="1676400"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="70" name="รูป 70"/>
+        <xdr:cNvPr id="74" name="รูป 74"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4559,11 +5362,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="9239250" y="21564600"/>
+    <xdr:pos x="9239250" y="25793700"/>
     <xdr:ext cx="4191000" cy="1676400"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="71" name="รูป 71"/>
+        <xdr:cNvPr id="75" name="รูป 75"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4708,11 +5511,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="23622000"/>
+    <xdr:pos x="285750" y="27851100"/>
     <xdr:ext cx="2857500" cy="228600"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="72" name="รูป 72"/>
+        <xdr:cNvPr id="76" name="รูป 76"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4749,11 +5552,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="285750" y="23907750"/>
+    <xdr:pos x="285750" y="28136850"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="73" name="รูป 73"/>
+        <xdr:cNvPr id="77" name="รูป 77"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4794,11 +5597,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="3619500" y="23907750"/>
+    <xdr:pos x="3619500" y="28136850"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="74" name="รูป 74"/>
+        <xdr:cNvPr id="78" name="รูป 78"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4839,11 +5642,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="6953250" y="23907750"/>
+    <xdr:pos x="6953250" y="28136850"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="75" name="รูป 75"/>
+        <xdr:cNvPr id="79" name="รูป 79"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4884,11 +5687,11 @@
     <xdr:clientData/>
   </xdr:absoluteAnchor>
   <xdr:absoluteAnchor>
-    <xdr:pos x="10287000" y="23907750"/>
+    <xdr:pos x="10287000" y="28136850"/>
     <xdr:ext cx="3143250" cy="381000"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="76" name="รูป 76"/>
+        <xdr:cNvPr id="80" name="รูป 80"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5116,7 +5919,7 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">OFAU 3.3 · รอบ 100 (2026-09-12)</t>
+          <t xml:space="preserve">OFAU 3.3 · รอบ 101 (2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -6449,7 +7252,7 @@
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 100 (2026-09-12))</t>
+          <t xml:space="preserve">เลขรุ่นที่เห็นตรงกับในโค้ด (ตอนสร้างไฟล์นี้คือ OFAU 3.3 · รอบ 101 (2026-09-12))</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="2">
